--- a/doc/Entité de la BCC.xlsx
+++ b/doc/Entité de la BCC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\actis-bcc\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34D87D77-88D9-42BB-BE6D-CEC17FF5A4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D622BC-9983-4866-A10F-672EA7AF29AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1455" windowWidth="29040" windowHeight="15720" xr2:uid="{FA0433DF-297A-4C25-98B3-2EF6E62C0A78}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId2"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="85">
   <si>
     <t>DG</t>
   </si>
@@ -238,13 +241,64 @@
   </si>
   <si>
     <t>Label Direction</t>
+  </si>
+  <si>
+    <t>Étiquettes de lignes</t>
+  </si>
+  <si>
+    <t>Total général</t>
+  </si>
+  <si>
+    <t>Direction de la Production</t>
+  </si>
+  <si>
+    <t>Direction Commerciale</t>
+  </si>
+  <si>
+    <t>Direction du Contrôle et Sécurité</t>
+  </si>
+  <si>
+    <t>Directions autonomes</t>
+  </si>
+  <si>
+    <t>Secrétariat Permanent de la Cellule Passation des Marchés</t>
+  </si>
+  <si>
+    <t>Direction de l'Inspection</t>
+  </si>
+  <si>
+    <t>Direction de la Caisse de Retraite</t>
+  </si>
+  <si>
+    <t>Direction de la Sûreté et Sécurité</t>
+  </si>
+  <si>
+    <t>Direction de la Stabilité Financière</t>
+  </si>
+  <si>
+    <t>Direction des Agréments</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>SPCPM</t>
+  </si>
+  <si>
+    <t>DCR</t>
+  </si>
+  <si>
+    <t>DSS</t>
+  </si>
+  <si>
+    <t>DSF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,8 +323,16 @@
       <color theme="1"/>
       <name val="Merriweather"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,6 +343,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1D9E75"/>
         <bgColor rgb="FF1D9E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -323,7 +397,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -332,8 +406,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -341,7 +440,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{63E2C9AC-3E83-4990-9CBE-BE6B951410A8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" indent="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -352,6 +458,426 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Utilisateur Windows" refreshedDate="46276.620369444441" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="25" xr:uid="{1066E57D-6588-4E3C-8848-7F70AA886931}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D26" sheet="Feuil1"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="DG" numFmtId="0">
+      <sharedItems count="7">
+        <s v="DGPM"/>
+        <s v="Gouv."/>
+        <s v="DGAS"/>
+        <s v="DGC"/>
+        <s v="DGSBF"/>
+        <s v="DGHM"/>
+        <s v="DGCEP"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="label DG" numFmtId="0">
+      <sharedItems count="7">
+        <s v="Direction Générale de la Politique Monétaire"/>
+        <s v="Gouverneur"/>
+        <s v="Direction Générale de l’Administration et des Services"/>
+        <s v="Direction Générale du Contrôle"/>
+        <s v="Direction Générale des Services Bancaires et Financiers"/>
+        <s v="Direction Générale de l’Hôtel de Monnaie"/>
+        <s v="Direction Générale des Études, de la Coordination et des Échanges Provinciaux"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Direction " numFmtId="0">
+      <sharedItems count="25">
+        <s v="DAE"/>
+        <s v="DRS"/>
+        <s v="DCOM"/>
+        <s v="DJ"/>
+        <s v="DCB"/>
+        <s v="DOBM"/>
+        <s v="DSOC"/>
+        <s v="DF"/>
+        <s v="DTIGP"/>
+        <s v="DRH"/>
+        <s v="DAI"/>
+        <s v="DCONF"/>
+        <s v="DGR"/>
+        <s v="DÉONTOLOGUE"/>
+        <s v="DSIF"/>
+        <s v="DSI"/>
+        <s v="RSSI"/>
+        <s v="DSSMP"/>
+        <s v="DR"/>
+        <s v="DIF"/>
+        <s v="DSG"/>
+        <s v="DT"/>
+        <s v="DCS"/>
+        <s v="DAF"/>
+        <s v="DACEP"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Label Direction" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="25">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Direction des Analyses Économiques"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Direction de la Recherche et des Statistiques"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Direction de la Communication"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Direction Juridique"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Direction du Contrôle Budgétaire"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Direction des Opérations Bancaires et des Marchés"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <s v="Direction de la Surveillance des Opérations de Change"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="7"/>
+    <s v="Direction Financière"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="8"/>
+    <s v="Direction des Travaux, des Infrastructures et de la Gestion du Patrimoine"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="9"/>
+    <s v="Direction des Ressources Humaines"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="10"/>
+    <s v="Direction de l’Audit Interne"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="11"/>
+    <s v="Direction de la Conformité"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="12"/>
+    <s v="Direction de la Gestion des Risques"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="13"/>
+    <s v="Déontologue"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="14"/>
+    <s v="Direction des Systèmes d’Information Financière"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="15"/>
+    <s v="Direction des Systèmes d’Information"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="16"/>
+    <s v="Responsable de la Sécurité des Systèmes d’Information"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="17"/>
+    <s v="Direction de la Supervision des Systèmes et Moyens de Paiement"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="18"/>
+    <s v="Direction de la Réglementation"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="19"/>
+    <s v="Direction des Institutions Financières"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="20"/>
+    <s v="Direction des Services Généraux"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="21"/>
+    <s v="Direction Technique"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="22"/>
+    <s v="Direction du Contrôle de la Sécurité"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="23"/>
+    <s v="Direction Administrative et Financière"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="24"/>
+    <s v="Direction de l’Administration et de la Coordination des Entités Provinciales"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6F6FE1CF-B91B-4189-B708-3345479644A6}" name="Tableau croisé dynamique1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H2:H35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="26">
+        <item x="24"/>
+        <item x="0"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item x="22"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="18"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="20"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="17"/>
+        <item x="21"/>
+        <item x="8"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="33">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -651,5251 +1177,5442 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78BF1153-9F5B-451D-AED0-67F78472FB95}">
-  <dimension ref="A1:D1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.54296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="65.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.7265625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="65.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H2" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H4" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H7" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H8" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H9" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H11" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H12" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H14" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H15" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H16" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H17" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H18" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H19" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H20" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="H21" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H22" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H23" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H24" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="39" x14ac:dyDescent="0.35">
+      <c r="H25" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="26" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34"/>
-      <c r="B34"/>
-      <c r="C34"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35"/>
-      <c r="B35"/>
-      <c r="C35"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36"/>
-      <c r="B36"/>
-      <c r="C36"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40"/>
-      <c r="B40"/>
-      <c r="C40"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41"/>
-      <c r="B41"/>
-      <c r="C41"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42"/>
-      <c r="B42"/>
-      <c r="C42"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="H26" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="E42" s="5"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43"/>
-      <c r="B43"/>
-      <c r="C43"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44"/>
-      <c r="B44"/>
-      <c r="C44"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="E44" s="5"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47"/>
-      <c r="B47"/>
-      <c r="C47"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48"/>
-      <c r="B48"/>
-      <c r="C48"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49"/>
-      <c r="B49"/>
-      <c r="C49"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50"/>
-      <c r="B50"/>
-      <c r="C50"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51"/>
-      <c r="B51"/>
-      <c r="C51"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52"/>
-      <c r="B52"/>
-      <c r="C52"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53"/>
-      <c r="B53"/>
-      <c r="C53"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55"/>
-      <c r="B55"/>
-      <c r="C55"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56"/>
-      <c r="B56"/>
-      <c r="C56"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57"/>
-      <c r="B57"/>
-      <c r="C57"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58"/>
-      <c r="B58"/>
-      <c r="C58"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59"/>
-      <c r="B59"/>
-      <c r="C59"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60"/>
-      <c r="B60"/>
-      <c r="C60"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61"/>
-      <c r="B61"/>
-      <c r="C61"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62"/>
-      <c r="B62"/>
-      <c r="C62"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63"/>
-      <c r="B63"/>
-      <c r="C63"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64"/>
-      <c r="B64"/>
-      <c r="C64"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65"/>
-      <c r="B65"/>
-      <c r="C65"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66"/>
-      <c r="B66"/>
-      <c r="C66"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67"/>
-      <c r="B67"/>
-      <c r="C67"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68"/>
-      <c r="B68"/>
-      <c r="C68"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69"/>
-      <c r="B69"/>
-      <c r="C69"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70"/>
-      <c r="B70"/>
-      <c r="C70"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71"/>
-      <c r="B71"/>
-      <c r="C71"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72"/>
-      <c r="B72"/>
-      <c r="C72"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73"/>
-      <c r="B73"/>
-      <c r="C73"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74"/>
-      <c r="B74"/>
-      <c r="C74"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75"/>
-      <c r="B75"/>
-      <c r="C75"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76"/>
-      <c r="B76"/>
-      <c r="C76"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77"/>
-      <c r="B77"/>
-      <c r="C77"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79"/>
-      <c r="B79"/>
-      <c r="C79"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80"/>
-      <c r="B80"/>
-      <c r="C80"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81"/>
-      <c r="B81"/>
-      <c r="C81"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82"/>
-      <c r="B82"/>
-      <c r="C82"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83"/>
-      <c r="B83"/>
-      <c r="C83"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84"/>
-      <c r="B84"/>
-      <c r="C84"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85"/>
-      <c r="B85"/>
-      <c r="C85"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86"/>
-      <c r="B86"/>
-      <c r="C86"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87"/>
-      <c r="B87"/>
-      <c r="C87"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88"/>
-      <c r="B88"/>
-      <c r="C88"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89"/>
-      <c r="B89"/>
-      <c r="C89"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90"/>
-      <c r="B90"/>
-      <c r="C90"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91"/>
-      <c r="B91"/>
-      <c r="C91"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93"/>
-      <c r="B93"/>
-      <c r="C93"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94"/>
-      <c r="B94"/>
-      <c r="C94"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95"/>
-      <c r="B95"/>
-      <c r="C95"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96"/>
-      <c r="B96"/>
-      <c r="C96"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97"/>
-      <c r="B97"/>
-      <c r="C97"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98"/>
-      <c r="B98"/>
-      <c r="C98"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99"/>
-      <c r="B99"/>
-      <c r="C99"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100"/>
-      <c r="B100"/>
-      <c r="C100"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101"/>
-      <c r="B101"/>
-      <c r="C101"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103"/>
-      <c r="B103"/>
-      <c r="C103"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104"/>
-      <c r="B104"/>
-      <c r="C104"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105"/>
-      <c r="B105"/>
-      <c r="C105"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106"/>
-      <c r="B106"/>
-      <c r="C106"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107"/>
-      <c r="B107"/>
-      <c r="C107"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108"/>
-      <c r="B108"/>
-      <c r="C108"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109"/>
-      <c r="B109"/>
-      <c r="C109"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110"/>
-      <c r="B110"/>
-      <c r="C110"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111"/>
-      <c r="B111"/>
-      <c r="C111"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112"/>
-      <c r="B112"/>
-      <c r="C112"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113"/>
-      <c r="B113"/>
-      <c r="C113"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114"/>
-      <c r="B114"/>
-      <c r="C114"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115"/>
-      <c r="B115"/>
-      <c r="C115"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116"/>
-      <c r="B116"/>
-      <c r="C116"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117"/>
-      <c r="B117"/>
-      <c r="C117"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118"/>
-      <c r="B118"/>
-      <c r="C118"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119"/>
-      <c r="B119"/>
-      <c r="C119"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120"/>
-      <c r="B120"/>
-      <c r="C120"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121"/>
-      <c r="B121"/>
-      <c r="C121"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122"/>
-      <c r="B122"/>
-      <c r="C122"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123"/>
-      <c r="B123"/>
-      <c r="C123"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124"/>
-      <c r="B124"/>
-      <c r="C124"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125"/>
-      <c r="B125"/>
-      <c r="C125"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126"/>
-      <c r="B126"/>
-      <c r="C126"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127"/>
-      <c r="B127"/>
-      <c r="C127"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128"/>
-      <c r="B128"/>
-      <c r="C128"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129"/>
-      <c r="B129"/>
-      <c r="C129"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130"/>
-      <c r="B130"/>
-      <c r="C130"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131"/>
-      <c r="B131"/>
-      <c r="C131"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132"/>
-      <c r="B132"/>
-      <c r="C132"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133"/>
-      <c r="B133"/>
-      <c r="C133"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134"/>
-      <c r="B134"/>
-      <c r="C134"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135"/>
-      <c r="B135"/>
-      <c r="C135"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136"/>
-      <c r="B136"/>
-      <c r="C136"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="5"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137"/>
-      <c r="B137"/>
-      <c r="C137"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138"/>
-      <c r="B138"/>
-      <c r="C138"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139"/>
-      <c r="B139"/>
-      <c r="C139"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140"/>
-      <c r="B140"/>
-      <c r="C140"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141"/>
-      <c r="B141"/>
-      <c r="C141"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142"/>
-      <c r="B142"/>
-      <c r="C142"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143"/>
-      <c r="B143"/>
-      <c r="C143"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="5"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144"/>
-      <c r="B144"/>
-      <c r="C144"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="5"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145"/>
-      <c r="B145"/>
-      <c r="C145"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146"/>
-      <c r="B146"/>
-      <c r="C146"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5"/>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147"/>
-      <c r="B147"/>
-      <c r="C147"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148"/>
-      <c r="B148"/>
-      <c r="C148"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149"/>
-      <c r="B149"/>
-      <c r="C149"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150"/>
-      <c r="B150"/>
-      <c r="C150"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151"/>
-      <c r="B151"/>
-      <c r="C151"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152"/>
-      <c r="B152"/>
-      <c r="C152"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153"/>
-      <c r="B153"/>
-      <c r="C153"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154"/>
-      <c r="B154"/>
-      <c r="C154"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155"/>
-      <c r="B155"/>
-      <c r="C155"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156"/>
-      <c r="B156"/>
-      <c r="C156"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157"/>
-      <c r="B157"/>
-      <c r="C157"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158"/>
-      <c r="B158"/>
-      <c r="C158"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="5"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159"/>
-      <c r="B159"/>
-      <c r="C159"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160"/>
-      <c r="B160"/>
-      <c r="C160"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="5"/>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161"/>
-      <c r="B161"/>
-      <c r="C161"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="5"/>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162"/>
-      <c r="B162"/>
-      <c r="C162"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="5"/>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163"/>
-      <c r="B163"/>
-      <c r="C163"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="5"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164"/>
-      <c r="B164"/>
-      <c r="C164"/>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165"/>
-      <c r="B165"/>
-      <c r="C165"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="5"/>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166"/>
-      <c r="B166"/>
-      <c r="C166"/>
+      <c r="B166" s="5"/>
+      <c r="C166" s="5"/>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167"/>
-      <c r="B167"/>
-      <c r="C167"/>
+      <c r="B167" s="5"/>
+      <c r="C167" s="5"/>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168"/>
-      <c r="B168"/>
-      <c r="C168"/>
+      <c r="B168" s="5"/>
+      <c r="C168" s="5"/>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169"/>
-      <c r="B169"/>
-      <c r="C169"/>
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170"/>
-      <c r="B170"/>
-      <c r="C170"/>
+      <c r="B170" s="5"/>
+      <c r="C170" s="5"/>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171"/>
-      <c r="B171"/>
-      <c r="C171"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="5"/>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172"/>
-      <c r="B172"/>
-      <c r="C172"/>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173"/>
-      <c r="B173"/>
-      <c r="C173"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="5"/>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174"/>
-      <c r="B174"/>
-      <c r="C174"/>
+      <c r="B174" s="5"/>
+      <c r="C174" s="5"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175"/>
-      <c r="B175"/>
-      <c r="C175"/>
+      <c r="B175" s="5"/>
+      <c r="C175" s="5"/>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176"/>
-      <c r="B176"/>
-      <c r="C176"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="5"/>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177"/>
-      <c r="B177"/>
-      <c r="C177"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="5"/>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178"/>
-      <c r="B178"/>
-      <c r="C178"/>
+      <c r="B178" s="5"/>
+      <c r="C178" s="5"/>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179"/>
-      <c r="B179"/>
-      <c r="C179"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="5"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180"/>
-      <c r="B180"/>
-      <c r="C180"/>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181"/>
-      <c r="B181"/>
-      <c r="C181"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="5"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182"/>
-      <c r="B182"/>
-      <c r="C182"/>
+      <c r="B182" s="5"/>
+      <c r="C182" s="5"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183"/>
-      <c r="B183"/>
-      <c r="C183"/>
+      <c r="B183" s="5"/>
+      <c r="C183" s="5"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184"/>
-      <c r="B184"/>
-      <c r="C184"/>
+      <c r="B184" s="5"/>
+      <c r="C184" s="5"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185"/>
-      <c r="B185"/>
-      <c r="C185"/>
+      <c r="B185" s="5"/>
+      <c r="C185" s="5"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186"/>
-      <c r="B186"/>
-      <c r="C186"/>
+      <c r="B186" s="5"/>
+      <c r="C186" s="5"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187"/>
-      <c r="B187"/>
-      <c r="C187"/>
+      <c r="B187" s="5"/>
+      <c r="C187" s="5"/>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188"/>
-      <c r="B188"/>
-      <c r="C188"/>
+      <c r="B188" s="5"/>
+      <c r="C188" s="5"/>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189"/>
-      <c r="B189"/>
-      <c r="C189"/>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190"/>
-      <c r="B190"/>
-      <c r="C190"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="5"/>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191"/>
-      <c r="B191"/>
-      <c r="C191"/>
+      <c r="B191" s="5"/>
+      <c r="C191" s="5"/>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192"/>
-      <c r="B192"/>
-      <c r="C192"/>
+      <c r="B192" s="5"/>
+      <c r="C192" s="5"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193"/>
-      <c r="B193"/>
-      <c r="C193"/>
+      <c r="B193" s="5"/>
+      <c r="C193" s="5"/>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194"/>
-      <c r="B194"/>
-      <c r="C194"/>
+      <c r="B194" s="5"/>
+      <c r="C194" s="5"/>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195"/>
-      <c r="B195"/>
-      <c r="C195"/>
+      <c r="B195" s="5"/>
+      <c r="C195" s="5"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196"/>
-      <c r="B196"/>
-      <c r="C196"/>
+      <c r="B196" s="5"/>
+      <c r="C196" s="5"/>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197"/>
-      <c r="B197"/>
-      <c r="C197"/>
+      <c r="B197" s="5"/>
+      <c r="C197" s="5"/>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198"/>
-      <c r="B198"/>
-      <c r="C198"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="5"/>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199"/>
-      <c r="B199"/>
-      <c r="C199"/>
+      <c r="B199" s="5"/>
+      <c r="C199" s="5"/>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200"/>
-      <c r="B200"/>
-      <c r="C200"/>
+      <c r="B200" s="5"/>
+      <c r="C200" s="5"/>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201"/>
-      <c r="B201"/>
-      <c r="C201"/>
+      <c r="B201" s="5"/>
+      <c r="C201" s="5"/>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202"/>
-      <c r="B202"/>
-      <c r="C202"/>
+      <c r="B202" s="5"/>
+      <c r="C202" s="5"/>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203"/>
-      <c r="B203"/>
-      <c r="C203"/>
+      <c r="B203" s="5"/>
+      <c r="C203" s="5"/>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204"/>
-      <c r="B204"/>
-      <c r="C204"/>
+      <c r="B204" s="5"/>
+      <c r="C204" s="5"/>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205"/>
-      <c r="B205"/>
-      <c r="C205"/>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206"/>
-      <c r="B206"/>
-      <c r="C206"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="5"/>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207"/>
-      <c r="B207"/>
-      <c r="C207"/>
+      <c r="B207" s="5"/>
+      <c r="C207" s="5"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208"/>
-      <c r="B208"/>
-      <c r="C208"/>
+      <c r="B208" s="5"/>
+      <c r="C208" s="5"/>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209"/>
-      <c r="B209"/>
-      <c r="C209"/>
+      <c r="B209" s="5"/>
+      <c r="C209" s="5"/>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210"/>
-      <c r="B210"/>
-      <c r="C210"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="5"/>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211"/>
-      <c r="B211"/>
-      <c r="C211"/>
+      <c r="B211" s="5"/>
+      <c r="C211" s="5"/>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212"/>
-      <c r="B212"/>
-      <c r="C212"/>
+      <c r="B212" s="5"/>
+      <c r="C212" s="5"/>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213"/>
-      <c r="B213"/>
-      <c r="C213"/>
+      <c r="B213" s="5"/>
+      <c r="C213" s="5"/>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214"/>
-      <c r="B214"/>
-      <c r="C214"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="5"/>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215"/>
-      <c r="B215"/>
-      <c r="C215"/>
+      <c r="B215" s="5"/>
+      <c r="C215" s="5"/>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216"/>
-      <c r="B216"/>
-      <c r="C216"/>
+      <c r="B216" s="5"/>
+      <c r="C216" s="5"/>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217"/>
-      <c r="B217"/>
-      <c r="C217"/>
+      <c r="B217" s="5"/>
+      <c r="C217" s="5"/>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218"/>
-      <c r="B218"/>
-      <c r="C218"/>
+      <c r="B218" s="5"/>
+      <c r="C218" s="5"/>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219"/>
-      <c r="B219"/>
-      <c r="C219"/>
+      <c r="B219" s="5"/>
+      <c r="C219" s="5"/>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220"/>
-      <c r="B220"/>
-      <c r="C220"/>
+      <c r="B220" s="5"/>
+      <c r="C220" s="5"/>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221"/>
-      <c r="B221"/>
-      <c r="C221"/>
+      <c r="B221" s="5"/>
+      <c r="C221" s="5"/>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222"/>
-      <c r="B222"/>
-      <c r="C222"/>
+      <c r="B222" s="5"/>
+      <c r="C222" s="5"/>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223"/>
-      <c r="B223"/>
-      <c r="C223"/>
+      <c r="B223" s="5"/>
+      <c r="C223" s="5"/>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224"/>
-      <c r="B224"/>
-      <c r="C224"/>
+      <c r="B224" s="5"/>
+      <c r="C224" s="5"/>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225"/>
-      <c r="B225"/>
-      <c r="C225"/>
+      <c r="B225" s="5"/>
+      <c r="C225" s="5"/>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226"/>
-      <c r="B226"/>
-      <c r="C226"/>
+      <c r="B226" s="5"/>
+      <c r="C226" s="5"/>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227"/>
-      <c r="B227"/>
-      <c r="C227"/>
+      <c r="B227" s="5"/>
+      <c r="C227" s="5"/>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228"/>
-      <c r="B228"/>
-      <c r="C228"/>
+      <c r="B228" s="5"/>
+      <c r="C228" s="5"/>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229"/>
-      <c r="B229"/>
-      <c r="C229"/>
+      <c r="B229" s="5"/>
+      <c r="C229" s="5"/>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230"/>
-      <c r="B230"/>
-      <c r="C230"/>
+      <c r="B230" s="5"/>
+      <c r="C230" s="5"/>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231"/>
-      <c r="B231"/>
-      <c r="C231"/>
+      <c r="B231" s="5"/>
+      <c r="C231" s="5"/>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232"/>
-      <c r="B232"/>
-      <c r="C232"/>
+      <c r="B232" s="5"/>
+      <c r="C232" s="5"/>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233"/>
-      <c r="B233"/>
-      <c r="C233"/>
+      <c r="B233" s="5"/>
+      <c r="C233" s="5"/>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234"/>
-      <c r="B234"/>
-      <c r="C234"/>
+      <c r="B234" s="5"/>
+      <c r="C234" s="5"/>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235"/>
-      <c r="B235"/>
-      <c r="C235"/>
+      <c r="B235" s="5"/>
+      <c r="C235" s="5"/>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236"/>
-      <c r="B236"/>
-      <c r="C236"/>
+      <c r="B236" s="5"/>
+      <c r="C236" s="5"/>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237"/>
-      <c r="B237"/>
-      <c r="C237"/>
+      <c r="B237" s="5"/>
+      <c r="C237" s="5"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238"/>
-      <c r="B238"/>
-      <c r="C238"/>
+      <c r="B238" s="5"/>
+      <c r="C238" s="5"/>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239"/>
-      <c r="B239"/>
-      <c r="C239"/>
+      <c r="B239" s="5"/>
+      <c r="C239" s="5"/>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240"/>
-      <c r="B240"/>
-      <c r="C240"/>
+      <c r="B240" s="5"/>
+      <c r="C240" s="5"/>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241"/>
-      <c r="B241"/>
-      <c r="C241"/>
+      <c r="B241" s="5"/>
+      <c r="C241" s="5"/>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242"/>
-      <c r="B242"/>
-      <c r="C242"/>
+      <c r="B242" s="5"/>
+      <c r="C242" s="5"/>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243"/>
-      <c r="B243"/>
-      <c r="C243"/>
+      <c r="B243" s="5"/>
+      <c r="C243" s="5"/>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244"/>
-      <c r="B244"/>
-      <c r="C244"/>
+      <c r="B244" s="5"/>
+      <c r="C244" s="5"/>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245"/>
-      <c r="B245"/>
-      <c r="C245"/>
+      <c r="B245" s="5"/>
+      <c r="C245" s="5"/>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246"/>
-      <c r="B246"/>
-      <c r="C246"/>
+      <c r="B246" s="5"/>
+      <c r="C246" s="5"/>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247"/>
-      <c r="B247"/>
-      <c r="C247"/>
+      <c r="B247" s="5"/>
+      <c r="C247" s="5"/>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248"/>
-      <c r="B248"/>
-      <c r="C248"/>
+      <c r="B248" s="5"/>
+      <c r="C248" s="5"/>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249"/>
-      <c r="B249"/>
-      <c r="C249"/>
+      <c r="B249" s="5"/>
+      <c r="C249" s="5"/>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250"/>
-      <c r="B250"/>
-      <c r="C250"/>
+      <c r="B250" s="5"/>
+      <c r="C250" s="5"/>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251"/>
-      <c r="B251"/>
-      <c r="C251"/>
+      <c r="B251" s="5"/>
+      <c r="C251" s="5"/>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252"/>
-      <c r="B252"/>
-      <c r="C252"/>
+      <c r="B252" s="5"/>
+      <c r="C252" s="5"/>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253"/>
-      <c r="B253"/>
-      <c r="C253"/>
+      <c r="B253" s="5"/>
+      <c r="C253" s="5"/>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254"/>
-      <c r="B254"/>
-      <c r="C254"/>
+      <c r="B254" s="5"/>
+      <c r="C254" s="5"/>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255"/>
-      <c r="B255"/>
-      <c r="C255"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="5"/>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256"/>
-      <c r="B256"/>
-      <c r="C256"/>
+      <c r="B256" s="5"/>
+      <c r="C256" s="5"/>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257"/>
-      <c r="B257"/>
-      <c r="C257"/>
+      <c r="B257" s="5"/>
+      <c r="C257" s="5"/>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258"/>
-      <c r="B258"/>
-      <c r="C258"/>
+      <c r="B258" s="5"/>
+      <c r="C258" s="5"/>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259"/>
-      <c r="B259"/>
-      <c r="C259"/>
+      <c r="B259" s="5"/>
+      <c r="C259" s="5"/>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260"/>
-      <c r="B260"/>
-      <c r="C260"/>
+      <c r="B260" s="5"/>
+      <c r="C260" s="5"/>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261"/>
-      <c r="B261"/>
-      <c r="C261"/>
+      <c r="B261" s="5"/>
+      <c r="C261" s="5"/>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262"/>
-      <c r="B262"/>
-      <c r="C262"/>
+      <c r="B262" s="5"/>
+      <c r="C262" s="5"/>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263"/>
-      <c r="B263"/>
-      <c r="C263"/>
+      <c r="B263" s="5"/>
+      <c r="C263" s="5"/>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264"/>
-      <c r="B264"/>
-      <c r="C264"/>
+      <c r="B264" s="5"/>
+      <c r="C264" s="5"/>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265"/>
-      <c r="B265"/>
-      <c r="C265"/>
+      <c r="B265" s="5"/>
+      <c r="C265" s="5"/>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266"/>
-      <c r="B266"/>
-      <c r="C266"/>
+      <c r="B266" s="5"/>
+      <c r="C266" s="5"/>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267"/>
-      <c r="B267"/>
-      <c r="C267"/>
+      <c r="B267" s="5"/>
+      <c r="C267" s="5"/>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268"/>
-      <c r="B268"/>
-      <c r="C268"/>
+      <c r="B268" s="5"/>
+      <c r="C268" s="5"/>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269"/>
-      <c r="B269"/>
-      <c r="C269"/>
+      <c r="B269" s="5"/>
+      <c r="C269" s="5"/>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270"/>
-      <c r="B270"/>
-      <c r="C270"/>
+      <c r="B270" s="5"/>
+      <c r="C270" s="5"/>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271"/>
-      <c r="B271"/>
-      <c r="C271"/>
+      <c r="B271" s="5"/>
+      <c r="C271" s="5"/>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272"/>
-      <c r="B272"/>
-      <c r="C272"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="5"/>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273"/>
-      <c r="B273"/>
-      <c r="C273"/>
+      <c r="B273" s="5"/>
+      <c r="C273" s="5"/>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274"/>
-      <c r="B274"/>
-      <c r="C274"/>
+      <c r="B274" s="5"/>
+      <c r="C274" s="5"/>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275"/>
-      <c r="B275"/>
-      <c r="C275"/>
+      <c r="B275" s="5"/>
+      <c r="C275" s="5"/>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276"/>
-      <c r="B276"/>
-      <c r="C276"/>
+      <c r="B276" s="5"/>
+      <c r="C276" s="5"/>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277"/>
-      <c r="B277"/>
-      <c r="C277"/>
+      <c r="B277" s="5"/>
+      <c r="C277" s="5"/>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278"/>
-      <c r="B278"/>
-      <c r="C278"/>
+      <c r="B278" s="5"/>
+      <c r="C278" s="5"/>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279"/>
-      <c r="B279"/>
-      <c r="C279"/>
+      <c r="B279" s="5"/>
+      <c r="C279" s="5"/>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280"/>
-      <c r="B280"/>
-      <c r="C280"/>
+      <c r="B280" s="5"/>
+      <c r="C280" s="5"/>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281"/>
-      <c r="B281"/>
-      <c r="C281"/>
+      <c r="B281" s="5"/>
+      <c r="C281" s="5"/>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282"/>
-      <c r="B282"/>
-      <c r="C282"/>
+      <c r="B282" s="5"/>
+      <c r="C282" s="5"/>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283"/>
-      <c r="B283"/>
-      <c r="C283"/>
+      <c r="B283" s="5"/>
+      <c r="C283" s="5"/>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284"/>
-      <c r="B284"/>
-      <c r="C284"/>
+      <c r="B284" s="5"/>
+      <c r="C284" s="5"/>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285"/>
-      <c r="B285"/>
-      <c r="C285"/>
+      <c r="B285" s="5"/>
+      <c r="C285" s="5"/>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286"/>
-      <c r="B286"/>
-      <c r="C286"/>
+      <c r="B286" s="5"/>
+      <c r="C286" s="5"/>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287"/>
-      <c r="B287"/>
-      <c r="C287"/>
+      <c r="B287" s="5"/>
+      <c r="C287" s="5"/>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288"/>
-      <c r="B288"/>
-      <c r="C288"/>
+      <c r="B288" s="5"/>
+      <c r="C288" s="5"/>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289"/>
-      <c r="B289"/>
-      <c r="C289"/>
+      <c r="B289" s="5"/>
+      <c r="C289" s="5"/>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290"/>
-      <c r="B290"/>
-      <c r="C290"/>
+      <c r="B290" s="5"/>
+      <c r="C290" s="5"/>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291"/>
-      <c r="B291"/>
-      <c r="C291"/>
+      <c r="B291" s="5"/>
+      <c r="C291" s="5"/>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292"/>
-      <c r="B292"/>
-      <c r="C292"/>
+      <c r="B292" s="5"/>
+      <c r="C292" s="5"/>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293"/>
-      <c r="B293"/>
-      <c r="C293"/>
+      <c r="B293" s="5"/>
+      <c r="C293" s="5"/>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294"/>
-      <c r="B294"/>
-      <c r="C294"/>
+      <c r="B294" s="5"/>
+      <c r="C294" s="5"/>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295"/>
-      <c r="B295"/>
-      <c r="C295"/>
+      <c r="B295" s="5"/>
+      <c r="C295" s="5"/>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296"/>
-      <c r="B296"/>
-      <c r="C296"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="5"/>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297"/>
-      <c r="B297"/>
-      <c r="C297"/>
+      <c r="B297" s="5"/>
+      <c r="C297" s="5"/>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298"/>
-      <c r="B298"/>
-      <c r="C298"/>
+      <c r="B298" s="5"/>
+      <c r="C298" s="5"/>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299"/>
-      <c r="B299"/>
-      <c r="C299"/>
+      <c r="B299" s="5"/>
+      <c r="C299" s="5"/>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300"/>
-      <c r="B300"/>
-      <c r="C300"/>
+      <c r="B300" s="5"/>
+      <c r="C300" s="5"/>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301"/>
-      <c r="B301"/>
-      <c r="C301"/>
+      <c r="B301" s="5"/>
+      <c r="C301" s="5"/>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302"/>
-      <c r="B302"/>
-      <c r="C302"/>
+      <c r="B302" s="5"/>
+      <c r="C302" s="5"/>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303"/>
-      <c r="B303"/>
-      <c r="C303"/>
+      <c r="B303" s="5"/>
+      <c r="C303" s="5"/>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304"/>
-      <c r="B304"/>
-      <c r="C304"/>
+      <c r="B304" s="5"/>
+      <c r="C304" s="5"/>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305"/>
-      <c r="B305"/>
-      <c r="C305"/>
+      <c r="B305" s="5"/>
+      <c r="C305" s="5"/>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306"/>
-      <c r="B306"/>
-      <c r="C306"/>
+      <c r="B306" s="5"/>
+      <c r="C306" s="5"/>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307"/>
-      <c r="B307"/>
-      <c r="C307"/>
+      <c r="B307" s="5"/>
+      <c r="C307" s="5"/>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308"/>
-      <c r="B308"/>
-      <c r="C308"/>
+      <c r="B308" s="5"/>
+      <c r="C308" s="5"/>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309"/>
-      <c r="B309"/>
-      <c r="C309"/>
+      <c r="B309" s="5"/>
+      <c r="C309" s="5"/>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310"/>
-      <c r="B310"/>
-      <c r="C310"/>
+      <c r="B310" s="5"/>
+      <c r="C310" s="5"/>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311"/>
-      <c r="B311"/>
-      <c r="C311"/>
+      <c r="B311" s="5"/>
+      <c r="C311" s="5"/>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312"/>
-      <c r="B312"/>
-      <c r="C312"/>
+      <c r="B312" s="5"/>
+      <c r="C312" s="5"/>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313"/>
-      <c r="B313"/>
-      <c r="C313"/>
+      <c r="B313" s="5"/>
+      <c r="C313" s="5"/>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314"/>
-      <c r="B314"/>
-      <c r="C314"/>
+      <c r="B314" s="5"/>
+      <c r="C314" s="5"/>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315"/>
-      <c r="B315"/>
-      <c r="C315"/>
+      <c r="B315" s="5"/>
+      <c r="C315" s="5"/>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316"/>
-      <c r="B316"/>
-      <c r="C316"/>
+      <c r="B316" s="5"/>
+      <c r="C316" s="5"/>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317"/>
-      <c r="B317"/>
-      <c r="C317"/>
+      <c r="B317" s="5"/>
+      <c r="C317" s="5"/>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318"/>
-      <c r="B318"/>
-      <c r="C318"/>
+      <c r="B318" s="5"/>
+      <c r="C318" s="5"/>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319"/>
-      <c r="B319"/>
-      <c r="C319"/>
+      <c r="B319" s="5"/>
+      <c r="C319" s="5"/>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320"/>
-      <c r="B320"/>
-      <c r="C320"/>
+      <c r="B320" s="5"/>
+      <c r="C320" s="5"/>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321"/>
-      <c r="B321"/>
-      <c r="C321"/>
+      <c r="B321" s="5"/>
+      <c r="C321" s="5"/>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322"/>
-      <c r="B322"/>
-      <c r="C322"/>
+      <c r="B322" s="5"/>
+      <c r="C322" s="5"/>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323"/>
-      <c r="B323"/>
-      <c r="C323"/>
+      <c r="B323" s="5"/>
+      <c r="C323" s="5"/>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324"/>
-      <c r="B324"/>
-      <c r="C324"/>
+      <c r="B324" s="5"/>
+      <c r="C324" s="5"/>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325"/>
-      <c r="B325"/>
-      <c r="C325"/>
+      <c r="B325" s="5"/>
+      <c r="C325" s="5"/>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326"/>
-      <c r="B326"/>
-      <c r="C326"/>
+      <c r="B326" s="5"/>
+      <c r="C326" s="5"/>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327"/>
-      <c r="B327"/>
-      <c r="C327"/>
+      <c r="B327" s="5"/>
+      <c r="C327" s="5"/>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328"/>
-      <c r="B328"/>
-      <c r="C328"/>
+      <c r="B328" s="5"/>
+      <c r="C328" s="5"/>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329"/>
-      <c r="B329"/>
-      <c r="C329"/>
+      <c r="B329" s="5"/>
+      <c r="C329" s="5"/>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330"/>
-      <c r="B330"/>
-      <c r="C330"/>
+      <c r="B330" s="5"/>
+      <c r="C330" s="5"/>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331"/>
-      <c r="B331"/>
-      <c r="C331"/>
+      <c r="B331" s="5"/>
+      <c r="C331" s="5"/>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332"/>
-      <c r="B332"/>
-      <c r="C332"/>
+      <c r="B332" s="5"/>
+      <c r="C332" s="5"/>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333"/>
-      <c r="B333"/>
-      <c r="C333"/>
+      <c r="B333" s="5"/>
+      <c r="C333" s="5"/>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334"/>
-      <c r="B334"/>
-      <c r="C334"/>
+      <c r="B334" s="5"/>
+      <c r="C334" s="5"/>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335"/>
-      <c r="B335"/>
-      <c r="C335"/>
+      <c r="B335" s="5"/>
+      <c r="C335" s="5"/>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336"/>
-      <c r="B336"/>
-      <c r="C336"/>
+      <c r="B336" s="5"/>
+      <c r="C336" s="5"/>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337"/>
-      <c r="B337"/>
-      <c r="C337"/>
+      <c r="B337" s="5"/>
+      <c r="C337" s="5"/>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338"/>
-      <c r="B338"/>
-      <c r="C338"/>
+      <c r="B338" s="5"/>
+      <c r="C338" s="5"/>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339"/>
-      <c r="B339"/>
-      <c r="C339"/>
+      <c r="B339" s="5"/>
+      <c r="C339" s="5"/>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340"/>
-      <c r="B340"/>
-      <c r="C340"/>
+      <c r="B340" s="5"/>
+      <c r="C340" s="5"/>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341"/>
-      <c r="B341"/>
-      <c r="C341"/>
+      <c r="B341" s="5"/>
+      <c r="C341" s="5"/>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342"/>
-      <c r="B342"/>
-      <c r="C342"/>
+      <c r="B342" s="5"/>
+      <c r="C342" s="5"/>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343"/>
-      <c r="B343"/>
-      <c r="C343"/>
+      <c r="B343" s="5"/>
+      <c r="C343" s="5"/>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344"/>
-      <c r="B344"/>
-      <c r="C344"/>
+      <c r="B344" s="5"/>
+      <c r="C344" s="5"/>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345"/>
-      <c r="B345"/>
-      <c r="C345"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="5"/>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346"/>
-      <c r="B346"/>
-      <c r="C346"/>
+      <c r="B346" s="5"/>
+      <c r="C346" s="5"/>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347"/>
-      <c r="B347"/>
-      <c r="C347"/>
+      <c r="B347" s="5"/>
+      <c r="C347" s="5"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348"/>
-      <c r="B348"/>
-      <c r="C348"/>
+      <c r="B348" s="5"/>
+      <c r="C348" s="5"/>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349"/>
-      <c r="B349"/>
-      <c r="C349"/>
+      <c r="B349" s="5"/>
+      <c r="C349" s="5"/>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350"/>
-      <c r="B350"/>
-      <c r="C350"/>
+      <c r="B350" s="5"/>
+      <c r="C350" s="5"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351"/>
-      <c r="B351"/>
-      <c r="C351"/>
+      <c r="B351" s="5"/>
+      <c r="C351" s="5"/>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352"/>
-      <c r="B352"/>
-      <c r="C352"/>
+      <c r="B352" s="5"/>
+      <c r="C352" s="5"/>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353"/>
-      <c r="B353"/>
-      <c r="C353"/>
+      <c r="B353" s="5"/>
+      <c r="C353" s="5"/>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354"/>
-      <c r="B354"/>
-      <c r="C354"/>
+      <c r="B354" s="5"/>
+      <c r="C354" s="5"/>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355"/>
-      <c r="B355"/>
-      <c r="C355"/>
+      <c r="B355" s="5"/>
+      <c r="C355" s="5"/>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356"/>
-      <c r="B356"/>
-      <c r="C356"/>
+      <c r="B356" s="5"/>
+      <c r="C356" s="5"/>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357"/>
-      <c r="B357"/>
-      <c r="C357"/>
+      <c r="B357" s="5"/>
+      <c r="C357" s="5"/>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358"/>
-      <c r="B358"/>
-      <c r="C358"/>
+      <c r="B358" s="5"/>
+      <c r="C358" s="5"/>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359"/>
-      <c r="B359"/>
-      <c r="C359"/>
+      <c r="B359" s="5"/>
+      <c r="C359" s="5"/>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360"/>
-      <c r="B360"/>
-      <c r="C360"/>
+      <c r="B360" s="5"/>
+      <c r="C360" s="5"/>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361"/>
-      <c r="B361"/>
-      <c r="C361"/>
+      <c r="B361" s="5"/>
+      <c r="C361" s="5"/>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362"/>
-      <c r="B362"/>
-      <c r="C362"/>
+      <c r="B362" s="5"/>
+      <c r="C362" s="5"/>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363"/>
-      <c r="B363"/>
-      <c r="C363"/>
+      <c r="B363" s="5"/>
+      <c r="C363" s="5"/>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364"/>
-      <c r="B364"/>
-      <c r="C364"/>
+      <c r="B364" s="5"/>
+      <c r="C364" s="5"/>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365"/>
-      <c r="B365"/>
-      <c r="C365"/>
+      <c r="B365" s="5"/>
+      <c r="C365" s="5"/>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366"/>
-      <c r="B366"/>
-      <c r="C366"/>
+      <c r="B366" s="5"/>
+      <c r="C366" s="5"/>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367"/>
-      <c r="B367"/>
-      <c r="C367"/>
+      <c r="B367" s="5"/>
+      <c r="C367" s="5"/>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368"/>
-      <c r="B368"/>
-      <c r="C368"/>
+      <c r="B368" s="5"/>
+      <c r="C368" s="5"/>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369"/>
-      <c r="B369"/>
-      <c r="C369"/>
+      <c r="B369" s="5"/>
+      <c r="C369" s="5"/>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370"/>
-      <c r="B370"/>
-      <c r="C370"/>
+      <c r="B370" s="5"/>
+      <c r="C370" s="5"/>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371"/>
-      <c r="B371"/>
-      <c r="C371"/>
+      <c r="B371" s="5"/>
+      <c r="C371" s="5"/>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372"/>
-      <c r="B372"/>
-      <c r="C372"/>
+      <c r="B372" s="5"/>
+      <c r="C372" s="5"/>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373"/>
-      <c r="B373"/>
-      <c r="C373"/>
+      <c r="B373" s="5"/>
+      <c r="C373" s="5"/>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374"/>
-      <c r="B374"/>
-      <c r="C374"/>
+      <c r="B374" s="5"/>
+      <c r="C374" s="5"/>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375"/>
-      <c r="B375"/>
-      <c r="C375"/>
+      <c r="B375" s="5"/>
+      <c r="C375" s="5"/>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376"/>
-      <c r="B376"/>
-      <c r="C376"/>
+      <c r="B376" s="5"/>
+      <c r="C376" s="5"/>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377"/>
-      <c r="B377"/>
-      <c r="C377"/>
+      <c r="B377" s="5"/>
+      <c r="C377" s="5"/>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378"/>
-      <c r="B378"/>
-      <c r="C378"/>
+      <c r="B378" s="5"/>
+      <c r="C378" s="5"/>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379"/>
-      <c r="B379"/>
-      <c r="C379"/>
+      <c r="B379" s="5"/>
+      <c r="C379" s="5"/>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380"/>
-      <c r="B380"/>
-      <c r="C380"/>
+      <c r="B380" s="5"/>
+      <c r="C380" s="5"/>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381"/>
-      <c r="B381"/>
-      <c r="C381"/>
+      <c r="B381" s="5"/>
+      <c r="C381" s="5"/>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382"/>
-      <c r="B382"/>
-      <c r="C382"/>
+      <c r="B382" s="5"/>
+      <c r="C382" s="5"/>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383"/>
-      <c r="B383"/>
-      <c r="C383"/>
+      <c r="B383" s="5"/>
+      <c r="C383" s="5"/>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384"/>
-      <c r="B384"/>
-      <c r="C384"/>
+      <c r="B384" s="5"/>
+      <c r="C384" s="5"/>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385"/>
-      <c r="B385"/>
-      <c r="C385"/>
+      <c r="B385" s="5"/>
+      <c r="C385" s="5"/>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386"/>
-      <c r="B386"/>
-      <c r="C386"/>
+      <c r="B386" s="5"/>
+      <c r="C386" s="5"/>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387"/>
-      <c r="B387"/>
-      <c r="C387"/>
+      <c r="B387" s="5"/>
+      <c r="C387" s="5"/>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388"/>
-      <c r="B388"/>
-      <c r="C388"/>
+      <c r="B388" s="5"/>
+      <c r="C388" s="5"/>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389"/>
-      <c r="B389"/>
-      <c r="C389"/>
+      <c r="B389" s="5"/>
+      <c r="C389" s="5"/>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390"/>
-      <c r="B390"/>
-      <c r="C390"/>
+      <c r="B390" s="5"/>
+      <c r="C390" s="5"/>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391"/>
-      <c r="B391"/>
-      <c r="C391"/>
+      <c r="B391" s="5"/>
+      <c r="C391" s="5"/>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392"/>
-      <c r="B392"/>
-      <c r="C392"/>
+      <c r="B392" s="5"/>
+      <c r="C392" s="5"/>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393"/>
-      <c r="B393"/>
-      <c r="C393"/>
+      <c r="B393" s="5"/>
+      <c r="C393" s="5"/>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394"/>
-      <c r="B394"/>
-      <c r="C394"/>
+      <c r="B394" s="5"/>
+      <c r="C394" s="5"/>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395"/>
-      <c r="B395"/>
-      <c r="C395"/>
+      <c r="B395" s="5"/>
+      <c r="C395" s="5"/>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396"/>
-      <c r="B396"/>
-      <c r="C396"/>
+      <c r="B396" s="5"/>
+      <c r="C396" s="5"/>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397"/>
-      <c r="B397"/>
-      <c r="C397"/>
+      <c r="B397" s="5"/>
+      <c r="C397" s="5"/>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398"/>
-      <c r="B398"/>
-      <c r="C398"/>
+      <c r="B398" s="5"/>
+      <c r="C398" s="5"/>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399"/>
-      <c r="B399"/>
-      <c r="C399"/>
+      <c r="B399" s="5"/>
+      <c r="C399" s="5"/>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400"/>
-      <c r="B400"/>
-      <c r="C400"/>
+      <c r="B400" s="5"/>
+      <c r="C400" s="5"/>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401"/>
-      <c r="B401"/>
-      <c r="C401"/>
+      <c r="B401" s="5"/>
+      <c r="C401" s="5"/>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402"/>
-      <c r="B402"/>
-      <c r="C402"/>
+      <c r="B402" s="5"/>
+      <c r="C402" s="5"/>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403"/>
-      <c r="B403"/>
-      <c r="C403"/>
+      <c r="B403" s="5"/>
+      <c r="C403" s="5"/>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404"/>
-      <c r="B404"/>
-      <c r="C404"/>
+      <c r="B404" s="5"/>
+      <c r="C404" s="5"/>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405"/>
-      <c r="B405"/>
-      <c r="C405"/>
+      <c r="B405" s="5"/>
+      <c r="C405" s="5"/>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406"/>
-      <c r="B406"/>
-      <c r="C406"/>
+      <c r="B406" s="5"/>
+      <c r="C406" s="5"/>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407"/>
-      <c r="B407"/>
-      <c r="C407"/>
+      <c r="B407" s="5"/>
+      <c r="C407" s="5"/>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408"/>
-      <c r="B408"/>
-      <c r="C408"/>
+      <c r="B408" s="5"/>
+      <c r="C408" s="5"/>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409"/>
-      <c r="B409"/>
-      <c r="C409"/>
+      <c r="B409" s="5"/>
+      <c r="C409" s="5"/>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410"/>
-      <c r="B410"/>
-      <c r="C410"/>
+      <c r="B410" s="5"/>
+      <c r="C410" s="5"/>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411"/>
-      <c r="B411"/>
-      <c r="C411"/>
+      <c r="B411" s="5"/>
+      <c r="C411" s="5"/>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412"/>
-      <c r="B412"/>
-      <c r="C412"/>
+      <c r="B412" s="5"/>
+      <c r="C412" s="5"/>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413"/>
-      <c r="B413"/>
-      <c r="C413"/>
+      <c r="B413" s="5"/>
+      <c r="C413" s="5"/>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414"/>
-      <c r="B414"/>
-      <c r="C414"/>
+      <c r="B414" s="5"/>
+      <c r="C414" s="5"/>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415"/>
-      <c r="B415"/>
-      <c r="C415"/>
+      <c r="B415" s="5"/>
+      <c r="C415" s="5"/>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416"/>
-      <c r="B416"/>
-      <c r="C416"/>
+      <c r="B416" s="5"/>
+      <c r="C416" s="5"/>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417"/>
-      <c r="B417"/>
-      <c r="C417"/>
+      <c r="B417" s="5"/>
+      <c r="C417" s="5"/>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418"/>
-      <c r="B418"/>
-      <c r="C418"/>
+      <c r="B418" s="5"/>
+      <c r="C418" s="5"/>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419"/>
-      <c r="B419"/>
-      <c r="C419"/>
+      <c r="B419" s="5"/>
+      <c r="C419" s="5"/>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420"/>
-      <c r="B420"/>
-      <c r="C420"/>
+      <c r="B420" s="5"/>
+      <c r="C420" s="5"/>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421"/>
-      <c r="B421"/>
-      <c r="C421"/>
+      <c r="B421" s="5"/>
+      <c r="C421" s="5"/>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422"/>
-      <c r="B422"/>
-      <c r="C422"/>
+      <c r="B422" s="5"/>
+      <c r="C422" s="5"/>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423"/>
-      <c r="B423"/>
-      <c r="C423"/>
+      <c r="B423" s="5"/>
+      <c r="C423" s="5"/>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424"/>
-      <c r="B424"/>
-      <c r="C424"/>
+      <c r="B424" s="5"/>
+      <c r="C424" s="5"/>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425"/>
-      <c r="B425"/>
-      <c r="C425"/>
+      <c r="B425" s="5"/>
+      <c r="C425" s="5"/>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426"/>
-      <c r="B426"/>
-      <c r="C426"/>
+      <c r="B426" s="5"/>
+      <c r="C426" s="5"/>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427"/>
-      <c r="B427"/>
-      <c r="C427"/>
+      <c r="B427" s="5"/>
+      <c r="C427" s="5"/>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428"/>
-      <c r="B428"/>
-      <c r="C428"/>
+      <c r="B428" s="5"/>
+      <c r="C428" s="5"/>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429"/>
-      <c r="B429"/>
-      <c r="C429"/>
+      <c r="B429" s="5"/>
+      <c r="C429" s="5"/>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430"/>
-      <c r="B430"/>
-      <c r="C430"/>
+      <c r="B430" s="5"/>
+      <c r="C430" s="5"/>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431"/>
-      <c r="B431"/>
-      <c r="C431"/>
+      <c r="B431" s="5"/>
+      <c r="C431" s="5"/>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432"/>
-      <c r="B432"/>
-      <c r="C432"/>
+      <c r="B432" s="5"/>
+      <c r="C432" s="5"/>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433"/>
-      <c r="B433"/>
-      <c r="C433"/>
+      <c r="B433" s="5"/>
+      <c r="C433" s="5"/>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434"/>
-      <c r="B434"/>
-      <c r="C434"/>
+      <c r="B434" s="5"/>
+      <c r="C434" s="5"/>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435"/>
-      <c r="B435"/>
-      <c r="C435"/>
+      <c r="B435" s="5"/>
+      <c r="C435" s="5"/>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436"/>
-      <c r="B436"/>
-      <c r="C436"/>
+      <c r="B436" s="5"/>
+      <c r="C436" s="5"/>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437"/>
-      <c r="B437"/>
-      <c r="C437"/>
+      <c r="B437" s="5"/>
+      <c r="C437" s="5"/>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438"/>
-      <c r="B438"/>
-      <c r="C438"/>
+      <c r="B438" s="5"/>
+      <c r="C438" s="5"/>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439"/>
-      <c r="B439"/>
-      <c r="C439"/>
+      <c r="B439" s="5"/>
+      <c r="C439" s="5"/>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440"/>
-      <c r="B440"/>
-      <c r="C440"/>
+      <c r="B440" s="5"/>
+      <c r="C440" s="5"/>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441"/>
-      <c r="B441"/>
-      <c r="C441"/>
+      <c r="B441" s="5"/>
+      <c r="C441" s="5"/>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442"/>
-      <c r="B442"/>
-      <c r="C442"/>
+      <c r="B442" s="5"/>
+      <c r="C442" s="5"/>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443"/>
-      <c r="B443"/>
-      <c r="C443"/>
+      <c r="B443" s="5"/>
+      <c r="C443" s="5"/>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444"/>
-      <c r="B444"/>
-      <c r="C444"/>
+      <c r="B444" s="5"/>
+      <c r="C444" s="5"/>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445"/>
-      <c r="B445"/>
-      <c r="C445"/>
+      <c r="B445" s="5"/>
+      <c r="C445" s="5"/>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446"/>
-      <c r="B446"/>
-      <c r="C446"/>
+      <c r="B446" s="5"/>
+      <c r="C446" s="5"/>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447"/>
-      <c r="B447"/>
-      <c r="C447"/>
+      <c r="B447" s="5"/>
+      <c r="C447" s="5"/>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448"/>
-      <c r="B448"/>
-      <c r="C448"/>
+      <c r="B448" s="5"/>
+      <c r="C448" s="5"/>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449"/>
-      <c r="B449"/>
-      <c r="C449"/>
+      <c r="B449" s="5"/>
+      <c r="C449" s="5"/>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450"/>
-      <c r="B450"/>
-      <c r="C450"/>
+      <c r="B450" s="5"/>
+      <c r="C450" s="5"/>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451"/>
-      <c r="B451"/>
-      <c r="C451"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="5"/>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452"/>
-      <c r="B452"/>
-      <c r="C452"/>
+      <c r="B452" s="5"/>
+      <c r="C452" s="5"/>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453"/>
-      <c r="B453"/>
-      <c r="C453"/>
+      <c r="B453" s="5"/>
+      <c r="C453" s="5"/>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454"/>
-      <c r="B454"/>
-      <c r="C454"/>
+      <c r="B454" s="5"/>
+      <c r="C454" s="5"/>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455"/>
-      <c r="B455"/>
-      <c r="C455"/>
+      <c r="B455" s="5"/>
+      <c r="C455" s="5"/>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456"/>
-      <c r="B456"/>
-      <c r="C456"/>
+      <c r="B456" s="5"/>
+      <c r="C456" s="5"/>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457"/>
-      <c r="B457"/>
-      <c r="C457"/>
+      <c r="B457" s="5"/>
+      <c r="C457" s="5"/>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458"/>
-      <c r="B458"/>
-      <c r="C458"/>
+      <c r="B458" s="5"/>
+      <c r="C458" s="5"/>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459"/>
-      <c r="B459"/>
-      <c r="C459"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="5"/>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460"/>
-      <c r="B460"/>
-      <c r="C460"/>
+      <c r="B460" s="5"/>
+      <c r="C460" s="5"/>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461"/>
-      <c r="B461"/>
-      <c r="C461"/>
+      <c r="B461" s="5"/>
+      <c r="C461" s="5"/>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462"/>
-      <c r="B462"/>
-      <c r="C462"/>
+      <c r="B462" s="5"/>
+      <c r="C462" s="5"/>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463"/>
-      <c r="B463"/>
-      <c r="C463"/>
+      <c r="B463" s="5"/>
+      <c r="C463" s="5"/>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464"/>
-      <c r="B464"/>
-      <c r="C464"/>
+      <c r="B464" s="5"/>
+      <c r="C464" s="5"/>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465"/>
-      <c r="B465"/>
-      <c r="C465"/>
+      <c r="B465" s="5"/>
+      <c r="C465" s="5"/>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466"/>
-      <c r="B466"/>
-      <c r="C466"/>
+      <c r="B466" s="5"/>
+      <c r="C466" s="5"/>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467"/>
-      <c r="B467"/>
-      <c r="C467"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="5"/>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468"/>
-      <c r="B468"/>
-      <c r="C468"/>
+      <c r="B468" s="5"/>
+      <c r="C468" s="5"/>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469"/>
-      <c r="B469"/>
-      <c r="C469"/>
+      <c r="B469" s="5"/>
+      <c r="C469" s="5"/>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470"/>
-      <c r="B470"/>
-      <c r="C470"/>
+      <c r="B470" s="5"/>
+      <c r="C470" s="5"/>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471"/>
-      <c r="B471"/>
-      <c r="C471"/>
+      <c r="B471" s="5"/>
+      <c r="C471" s="5"/>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472"/>
-      <c r="B472"/>
-      <c r="C472"/>
+      <c r="B472" s="5"/>
+      <c r="C472" s="5"/>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473"/>
-      <c r="B473"/>
-      <c r="C473"/>
+      <c r="B473" s="5"/>
+      <c r="C473" s="5"/>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474"/>
-      <c r="B474"/>
-      <c r="C474"/>
+      <c r="B474" s="5"/>
+      <c r="C474" s="5"/>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475"/>
-      <c r="B475"/>
-      <c r="C475"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="5"/>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476"/>
-      <c r="B476"/>
-      <c r="C476"/>
+      <c r="B476" s="5"/>
+      <c r="C476" s="5"/>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477"/>
-      <c r="B477"/>
-      <c r="C477"/>
+      <c r="B477" s="5"/>
+      <c r="C477" s="5"/>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478"/>
-      <c r="B478"/>
-      <c r="C478"/>
+      <c r="B478" s="5"/>
+      <c r="C478" s="5"/>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479"/>
-      <c r="B479"/>
-      <c r="C479"/>
+      <c r="B479" s="5"/>
+      <c r="C479" s="5"/>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480"/>
-      <c r="B480"/>
-      <c r="C480"/>
+      <c r="B480" s="5"/>
+      <c r="C480" s="5"/>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481"/>
-      <c r="B481"/>
-      <c r="C481"/>
+      <c r="B481" s="5"/>
+      <c r="C481" s="5"/>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482"/>
-      <c r="B482"/>
-      <c r="C482"/>
+      <c r="B482" s="5"/>
+      <c r="C482" s="5"/>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483"/>
-      <c r="B483"/>
-      <c r="C483"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="5"/>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484"/>
-      <c r="B484"/>
-      <c r="C484"/>
+      <c r="B484" s="5"/>
+      <c r="C484" s="5"/>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485"/>
-      <c r="B485"/>
-      <c r="C485"/>
+      <c r="B485" s="5"/>
+      <c r="C485" s="5"/>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486"/>
-      <c r="B486"/>
-      <c r="C486"/>
+      <c r="B486" s="5"/>
+      <c r="C486" s="5"/>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487"/>
-      <c r="B487"/>
-      <c r="C487"/>
+      <c r="B487" s="5"/>
+      <c r="C487" s="5"/>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488"/>
-      <c r="B488"/>
-      <c r="C488"/>
+      <c r="B488" s="5"/>
+      <c r="C488" s="5"/>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489"/>
-      <c r="B489"/>
-      <c r="C489"/>
+      <c r="B489" s="5"/>
+      <c r="C489" s="5"/>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490"/>
-      <c r="B490"/>
-      <c r="C490"/>
+      <c r="B490" s="5"/>
+      <c r="C490" s="5"/>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491"/>
-      <c r="B491"/>
-      <c r="C491"/>
+      <c r="B491" s="5"/>
+      <c r="C491" s="5"/>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492"/>
-      <c r="B492"/>
-      <c r="C492"/>
+      <c r="B492" s="5"/>
+      <c r="C492" s="5"/>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493"/>
-      <c r="B493"/>
-      <c r="C493"/>
+      <c r="B493" s="5"/>
+      <c r="C493" s="5"/>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494"/>
-      <c r="B494"/>
-      <c r="C494"/>
+      <c r="B494" s="5"/>
+      <c r="C494" s="5"/>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495"/>
-      <c r="B495"/>
-      <c r="C495"/>
+      <c r="B495" s="5"/>
+      <c r="C495" s="5"/>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496"/>
-      <c r="B496"/>
-      <c r="C496"/>
+      <c r="B496" s="5"/>
+      <c r="C496" s="5"/>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497"/>
-      <c r="B497"/>
-      <c r="C497"/>
+      <c r="B497" s="5"/>
+      <c r="C497" s="5"/>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498"/>
-      <c r="B498"/>
-      <c r="C498"/>
+      <c r="B498" s="5"/>
+      <c r="C498" s="5"/>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499"/>
-      <c r="B499"/>
-      <c r="C499"/>
+      <c r="B499" s="5"/>
+      <c r="C499" s="5"/>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500"/>
-      <c r="B500"/>
-      <c r="C500"/>
+      <c r="B500" s="5"/>
+      <c r="C500" s="5"/>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501"/>
-      <c r="B501"/>
-      <c r="C501"/>
+      <c r="B501" s="5"/>
+      <c r="C501" s="5"/>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502"/>
-      <c r="B502"/>
-      <c r="C502"/>
+      <c r="B502" s="5"/>
+      <c r="C502" s="5"/>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503"/>
-      <c r="B503"/>
-      <c r="C503"/>
+      <c r="B503" s="5"/>
+      <c r="C503" s="5"/>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504"/>
-      <c r="B504"/>
-      <c r="C504"/>
+      <c r="B504" s="5"/>
+      <c r="C504" s="5"/>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A505"/>
-      <c r="B505"/>
-      <c r="C505"/>
+      <c r="B505" s="5"/>
+      <c r="C505" s="5"/>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A506"/>
-      <c r="B506"/>
-      <c r="C506"/>
+      <c r="B506" s="5"/>
+      <c r="C506" s="5"/>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A507"/>
-      <c r="B507"/>
-      <c r="C507"/>
+      <c r="B507" s="5"/>
+      <c r="C507" s="5"/>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A508"/>
-      <c r="B508"/>
-      <c r="C508"/>
+      <c r="B508" s="5"/>
+      <c r="C508" s="5"/>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A509"/>
-      <c r="B509"/>
-      <c r="C509"/>
+      <c r="B509" s="5"/>
+      <c r="C509" s="5"/>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A510"/>
-      <c r="B510"/>
-      <c r="C510"/>
+      <c r="B510" s="5"/>
+      <c r="C510" s="5"/>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A511"/>
-      <c r="B511"/>
-      <c r="C511"/>
+      <c r="B511" s="5"/>
+      <c r="C511" s="5"/>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A512"/>
-      <c r="B512"/>
-      <c r="C512"/>
+      <c r="B512" s="5"/>
+      <c r="C512" s="5"/>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A513"/>
-      <c r="B513"/>
-      <c r="C513"/>
+      <c r="B513" s="5"/>
+      <c r="C513" s="5"/>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A514"/>
-      <c r="B514"/>
-      <c r="C514"/>
+      <c r="B514" s="5"/>
+      <c r="C514" s="5"/>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A515"/>
-      <c r="B515"/>
-      <c r="C515"/>
+      <c r="B515" s="5"/>
+      <c r="C515" s="5"/>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A516"/>
-      <c r="B516"/>
-      <c r="C516"/>
+      <c r="B516" s="5"/>
+      <c r="C516" s="5"/>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A517"/>
-      <c r="B517"/>
-      <c r="C517"/>
+      <c r="B517" s="5"/>
+      <c r="C517" s="5"/>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A518"/>
-      <c r="B518"/>
-      <c r="C518"/>
+      <c r="B518" s="5"/>
+      <c r="C518" s="5"/>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A519"/>
-      <c r="B519"/>
-      <c r="C519"/>
+      <c r="B519" s="5"/>
+      <c r="C519" s="5"/>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A520"/>
-      <c r="B520"/>
-      <c r="C520"/>
+      <c r="B520" s="5"/>
+      <c r="C520" s="5"/>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A521"/>
-      <c r="B521"/>
-      <c r="C521"/>
+      <c r="B521" s="5"/>
+      <c r="C521" s="5"/>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A522"/>
-      <c r="B522"/>
-      <c r="C522"/>
+      <c r="B522" s="5"/>
+      <c r="C522" s="5"/>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523"/>
-      <c r="B523"/>
-      <c r="C523"/>
+      <c r="B523" s="5"/>
+      <c r="C523" s="5"/>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A524"/>
-      <c r="B524"/>
-      <c r="C524"/>
+      <c r="B524" s="5"/>
+      <c r="C524" s="5"/>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A525"/>
-      <c r="B525"/>
-      <c r="C525"/>
+      <c r="B525" s="5"/>
+      <c r="C525" s="5"/>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A526"/>
-      <c r="B526"/>
-      <c r="C526"/>
+      <c r="B526" s="5"/>
+      <c r="C526" s="5"/>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A527"/>
-      <c r="B527"/>
-      <c r="C527"/>
+      <c r="B527" s="5"/>
+      <c r="C527" s="5"/>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A528"/>
-      <c r="B528"/>
-      <c r="C528"/>
+      <c r="B528" s="5"/>
+      <c r="C528" s="5"/>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A529"/>
-      <c r="B529"/>
-      <c r="C529"/>
+      <c r="B529" s="5"/>
+      <c r="C529" s="5"/>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A530"/>
-      <c r="B530"/>
-      <c r="C530"/>
+      <c r="B530" s="5"/>
+      <c r="C530" s="5"/>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A531"/>
-      <c r="B531"/>
-      <c r="C531"/>
+      <c r="B531" s="5"/>
+      <c r="C531" s="5"/>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A532"/>
-      <c r="B532"/>
-      <c r="C532"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="5"/>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A533"/>
-      <c r="B533"/>
-      <c r="C533"/>
+      <c r="B533" s="5"/>
+      <c r="C533" s="5"/>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A534"/>
-      <c r="B534"/>
-      <c r="C534"/>
+      <c r="B534" s="5"/>
+      <c r="C534" s="5"/>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A535"/>
-      <c r="B535"/>
-      <c r="C535"/>
+      <c r="B535" s="5"/>
+      <c r="C535" s="5"/>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A536"/>
-      <c r="B536"/>
-      <c r="C536"/>
+      <c r="B536" s="5"/>
+      <c r="C536" s="5"/>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A537"/>
-      <c r="B537"/>
-      <c r="C537"/>
+      <c r="B537" s="5"/>
+      <c r="C537" s="5"/>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A538"/>
-      <c r="B538"/>
-      <c r="C538"/>
+      <c r="B538" s="5"/>
+      <c r="C538" s="5"/>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A539"/>
-      <c r="B539"/>
-      <c r="C539"/>
+      <c r="B539" s="5"/>
+      <c r="C539" s="5"/>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A540"/>
-      <c r="B540"/>
-      <c r="C540"/>
+      <c r="B540" s="5"/>
+      <c r="C540" s="5"/>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A541"/>
-      <c r="B541"/>
-      <c r="C541"/>
+      <c r="B541" s="5"/>
+      <c r="C541" s="5"/>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A542"/>
-      <c r="B542"/>
-      <c r="C542"/>
+      <c r="B542" s="5"/>
+      <c r="C542" s="5"/>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A543"/>
-      <c r="B543"/>
-      <c r="C543"/>
+      <c r="B543" s="5"/>
+      <c r="C543" s="5"/>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A544"/>
-      <c r="B544"/>
-      <c r="C544"/>
+      <c r="B544" s="5"/>
+      <c r="C544" s="5"/>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A545"/>
-      <c r="B545"/>
-      <c r="C545"/>
+      <c r="B545" s="5"/>
+      <c r="C545" s="5"/>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A546"/>
-      <c r="B546"/>
-      <c r="C546"/>
+      <c r="B546" s="5"/>
+      <c r="C546" s="5"/>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A547"/>
-      <c r="B547"/>
-      <c r="C547"/>
+      <c r="B547" s="5"/>
+      <c r="C547" s="5"/>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A548"/>
-      <c r="B548"/>
-      <c r="C548"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="5"/>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A549"/>
-      <c r="B549"/>
-      <c r="C549"/>
+      <c r="B549" s="5"/>
+      <c r="C549" s="5"/>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A550"/>
-      <c r="B550"/>
-      <c r="C550"/>
+      <c r="B550" s="5"/>
+      <c r="C550" s="5"/>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A551"/>
-      <c r="B551"/>
-      <c r="C551"/>
+      <c r="B551" s="5"/>
+      <c r="C551" s="5"/>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A552"/>
-      <c r="B552"/>
-      <c r="C552"/>
+      <c r="B552" s="5"/>
+      <c r="C552" s="5"/>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A553"/>
-      <c r="B553"/>
-      <c r="C553"/>
+      <c r="B553" s="5"/>
+      <c r="C553" s="5"/>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A554"/>
-      <c r="B554"/>
-      <c r="C554"/>
+      <c r="B554" s="5"/>
+      <c r="C554" s="5"/>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A555"/>
-      <c r="B555"/>
-      <c r="C555"/>
+      <c r="B555" s="5"/>
+      <c r="C555" s="5"/>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A556"/>
-      <c r="B556"/>
-      <c r="C556"/>
+      <c r="B556" s="5"/>
+      <c r="C556" s="5"/>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A557"/>
-      <c r="B557"/>
-      <c r="C557"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="5"/>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A558"/>
-      <c r="B558"/>
-      <c r="C558"/>
+      <c r="B558" s="5"/>
+      <c r="C558" s="5"/>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A559"/>
-      <c r="B559"/>
-      <c r="C559"/>
+      <c r="B559" s="5"/>
+      <c r="C559" s="5"/>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A560"/>
-      <c r="B560"/>
-      <c r="C560"/>
+      <c r="B560" s="5"/>
+      <c r="C560" s="5"/>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A561"/>
-      <c r="B561"/>
-      <c r="C561"/>
+      <c r="B561" s="5"/>
+      <c r="C561" s="5"/>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A562"/>
-      <c r="B562"/>
-      <c r="C562"/>
+      <c r="B562" s="5"/>
+      <c r="C562" s="5"/>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A563"/>
-      <c r="B563"/>
-      <c r="C563"/>
+      <c r="B563" s="5"/>
+      <c r="C563" s="5"/>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A564"/>
-      <c r="B564"/>
-      <c r="C564"/>
+      <c r="B564" s="5"/>
+      <c r="C564" s="5"/>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A565"/>
-      <c r="B565"/>
-      <c r="C565"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="5"/>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A566"/>
-      <c r="B566"/>
-      <c r="C566"/>
+      <c r="B566" s="5"/>
+      <c r="C566" s="5"/>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A567"/>
-      <c r="B567"/>
-      <c r="C567"/>
+      <c r="B567" s="5"/>
+      <c r="C567" s="5"/>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A568"/>
-      <c r="B568"/>
-      <c r="C568"/>
+      <c r="B568" s="5"/>
+      <c r="C568" s="5"/>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A569"/>
-      <c r="B569"/>
-      <c r="C569"/>
+      <c r="B569" s="5"/>
+      <c r="C569" s="5"/>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A570"/>
-      <c r="B570"/>
-      <c r="C570"/>
+      <c r="B570" s="5"/>
+      <c r="C570" s="5"/>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A571"/>
-      <c r="B571"/>
-      <c r="C571"/>
+      <c r="B571" s="5"/>
+      <c r="C571" s="5"/>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A572"/>
-      <c r="B572"/>
-      <c r="C572"/>
+      <c r="B572" s="5"/>
+      <c r="C572" s="5"/>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A573"/>
-      <c r="B573"/>
-      <c r="C573"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="5"/>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A574"/>
-      <c r="B574"/>
-      <c r="C574"/>
+      <c r="B574" s="5"/>
+      <c r="C574" s="5"/>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A575"/>
-      <c r="B575"/>
-      <c r="C575"/>
+      <c r="B575" s="5"/>
+      <c r="C575" s="5"/>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A576"/>
-      <c r="B576"/>
-      <c r="C576"/>
+      <c r="B576" s="5"/>
+      <c r="C576" s="5"/>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A577"/>
-      <c r="B577"/>
-      <c r="C577"/>
+      <c r="B577" s="5"/>
+      <c r="C577" s="5"/>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A578"/>
-      <c r="B578"/>
-      <c r="C578"/>
+      <c r="B578" s="5"/>
+      <c r="C578" s="5"/>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A579"/>
-      <c r="B579"/>
-      <c r="C579"/>
+      <c r="B579" s="5"/>
+      <c r="C579" s="5"/>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A580"/>
-      <c r="B580"/>
-      <c r="C580"/>
+      <c r="B580" s="5"/>
+      <c r="C580" s="5"/>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A581"/>
-      <c r="B581"/>
-      <c r="C581"/>
+      <c r="B581" s="5"/>
+      <c r="C581" s="5"/>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A582"/>
-      <c r="B582"/>
-      <c r="C582"/>
+      <c r="B582" s="5"/>
+      <c r="C582" s="5"/>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A583"/>
-      <c r="B583"/>
-      <c r="C583"/>
+      <c r="B583" s="5"/>
+      <c r="C583" s="5"/>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A584"/>
-      <c r="B584"/>
-      <c r="C584"/>
+      <c r="B584" s="5"/>
+      <c r="C584" s="5"/>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A585"/>
-      <c r="B585"/>
-      <c r="C585"/>
+      <c r="B585" s="5"/>
+      <c r="C585" s="5"/>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A586"/>
-      <c r="B586"/>
-      <c r="C586"/>
+      <c r="B586" s="5"/>
+      <c r="C586" s="5"/>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A587"/>
-      <c r="B587"/>
-      <c r="C587"/>
+      <c r="B587" s="5"/>
+      <c r="C587" s="5"/>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A588"/>
-      <c r="B588"/>
-      <c r="C588"/>
+      <c r="B588" s="5"/>
+      <c r="C588" s="5"/>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A589"/>
-      <c r="B589"/>
-      <c r="C589"/>
+      <c r="B589" s="5"/>
+      <c r="C589" s="5"/>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A590"/>
-      <c r="B590"/>
-      <c r="C590"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="5"/>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A591"/>
-      <c r="B591"/>
-      <c r="C591"/>
+      <c r="B591" s="5"/>
+      <c r="C591" s="5"/>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A592"/>
-      <c r="B592"/>
-      <c r="C592"/>
+      <c r="B592" s="5"/>
+      <c r="C592" s="5"/>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A593"/>
-      <c r="B593"/>
-      <c r="C593"/>
+      <c r="B593" s="5"/>
+      <c r="C593" s="5"/>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A594"/>
-      <c r="B594"/>
-      <c r="C594"/>
+      <c r="B594" s="5"/>
+      <c r="C594" s="5"/>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A595"/>
-      <c r="B595"/>
-      <c r="C595"/>
+      <c r="B595" s="5"/>
+      <c r="C595" s="5"/>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A596"/>
-      <c r="B596"/>
-      <c r="C596"/>
+      <c r="B596" s="5"/>
+      <c r="C596" s="5"/>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A597"/>
-      <c r="B597"/>
-      <c r="C597"/>
+      <c r="B597" s="5"/>
+      <c r="C597" s="5"/>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A598"/>
-      <c r="B598"/>
-      <c r="C598"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="5"/>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A599"/>
-      <c r="B599"/>
-      <c r="C599"/>
+      <c r="B599" s="5"/>
+      <c r="C599" s="5"/>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A600"/>
-      <c r="B600"/>
-      <c r="C600"/>
+      <c r="B600" s="5"/>
+      <c r="C600" s="5"/>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A601"/>
-      <c r="B601"/>
-      <c r="C601"/>
+      <c r="B601" s="5"/>
+      <c r="C601" s="5"/>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A602"/>
-      <c r="B602"/>
-      <c r="C602"/>
+      <c r="B602" s="5"/>
+      <c r="C602" s="5"/>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A603"/>
-      <c r="B603"/>
-      <c r="C603"/>
+      <c r="B603" s="5"/>
+      <c r="C603" s="5"/>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A604"/>
-      <c r="B604"/>
-      <c r="C604"/>
+      <c r="B604" s="5"/>
+      <c r="C604" s="5"/>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A605"/>
-      <c r="B605"/>
-      <c r="C605"/>
+      <c r="B605" s="5"/>
+      <c r="C605" s="5"/>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A606"/>
-      <c r="B606"/>
-      <c r="C606"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="5"/>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A607"/>
-      <c r="B607"/>
-      <c r="C607"/>
+      <c r="B607" s="5"/>
+      <c r="C607" s="5"/>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A608"/>
-      <c r="B608"/>
-      <c r="C608"/>
+      <c r="B608" s="5"/>
+      <c r="C608" s="5"/>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A609"/>
-      <c r="B609"/>
-      <c r="C609"/>
+      <c r="B609" s="5"/>
+      <c r="C609" s="5"/>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A610"/>
-      <c r="B610"/>
-      <c r="C610"/>
+      <c r="B610" s="5"/>
+      <c r="C610" s="5"/>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A611"/>
-      <c r="B611"/>
-      <c r="C611"/>
+      <c r="B611" s="5"/>
+      <c r="C611" s="5"/>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A612"/>
-      <c r="B612"/>
-      <c r="C612"/>
+      <c r="B612" s="5"/>
+      <c r="C612" s="5"/>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A613"/>
-      <c r="B613"/>
-      <c r="C613"/>
+      <c r="B613" s="5"/>
+      <c r="C613" s="5"/>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A614"/>
-      <c r="B614"/>
-      <c r="C614"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="5"/>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A615"/>
-      <c r="B615"/>
-      <c r="C615"/>
+      <c r="B615" s="5"/>
+      <c r="C615" s="5"/>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A616"/>
-      <c r="B616"/>
-      <c r="C616"/>
+      <c r="B616" s="5"/>
+      <c r="C616" s="5"/>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A617"/>
-      <c r="B617"/>
-      <c r="C617"/>
+      <c r="B617" s="5"/>
+      <c r="C617" s="5"/>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A618"/>
-      <c r="B618"/>
-      <c r="C618"/>
+      <c r="B618" s="5"/>
+      <c r="C618" s="5"/>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A619"/>
-      <c r="B619"/>
-      <c r="C619"/>
+      <c r="B619" s="5"/>
+      <c r="C619" s="5"/>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A620"/>
-      <c r="B620"/>
-      <c r="C620"/>
+      <c r="B620" s="5"/>
+      <c r="C620" s="5"/>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A621"/>
-      <c r="B621"/>
-      <c r="C621"/>
+      <c r="B621" s="5"/>
+      <c r="C621" s="5"/>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A622"/>
-      <c r="B622"/>
-      <c r="C622"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="5"/>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A623"/>
-      <c r="B623"/>
-      <c r="C623"/>
+      <c r="B623" s="5"/>
+      <c r="C623" s="5"/>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A624"/>
-      <c r="B624"/>
-      <c r="C624"/>
+      <c r="B624" s="5"/>
+      <c r="C624" s="5"/>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A625"/>
-      <c r="B625"/>
-      <c r="C625"/>
+      <c r="B625" s="5"/>
+      <c r="C625" s="5"/>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A626"/>
-      <c r="B626"/>
-      <c r="C626"/>
+      <c r="B626" s="5"/>
+      <c r="C626" s="5"/>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A627"/>
-      <c r="B627"/>
-      <c r="C627"/>
+      <c r="B627" s="5"/>
+      <c r="C627" s="5"/>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A628"/>
-      <c r="B628"/>
-      <c r="C628"/>
+      <c r="B628" s="5"/>
+      <c r="C628" s="5"/>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A629"/>
-      <c r="B629"/>
-      <c r="C629"/>
+      <c r="B629" s="5"/>
+      <c r="C629" s="5"/>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A630"/>
-      <c r="B630"/>
-      <c r="C630"/>
+      <c r="B630" s="5"/>
+      <c r="C630" s="5"/>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A631"/>
-      <c r="B631"/>
-      <c r="C631"/>
+      <c r="B631" s="5"/>
+      <c r="C631" s="5"/>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A632"/>
-      <c r="B632"/>
-      <c r="C632"/>
+      <c r="B632" s="5"/>
+      <c r="C632" s="5"/>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A633"/>
-      <c r="B633"/>
-      <c r="C633"/>
+      <c r="B633" s="5"/>
+      <c r="C633" s="5"/>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A634"/>
-      <c r="B634"/>
-      <c r="C634"/>
+      <c r="B634" s="5"/>
+      <c r="C634" s="5"/>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A635"/>
-      <c r="B635"/>
-      <c r="C635"/>
+      <c r="B635" s="5"/>
+      <c r="C635" s="5"/>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A636"/>
-      <c r="B636"/>
-      <c r="C636"/>
+      <c r="B636" s="5"/>
+      <c r="C636" s="5"/>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A637"/>
-      <c r="B637"/>
-      <c r="C637"/>
+      <c r="B637" s="5"/>
+      <c r="C637" s="5"/>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A638"/>
-      <c r="B638"/>
-      <c r="C638"/>
+      <c r="B638" s="5"/>
+      <c r="C638" s="5"/>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A639"/>
-      <c r="B639"/>
-      <c r="C639"/>
+      <c r="B639" s="5"/>
+      <c r="C639" s="5"/>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A640"/>
-      <c r="B640"/>
-      <c r="C640"/>
+      <c r="B640" s="5"/>
+      <c r="C640" s="5"/>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A641"/>
-      <c r="B641"/>
-      <c r="C641"/>
+      <c r="B641" s="5"/>
+      <c r="C641" s="5"/>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A642"/>
-      <c r="B642"/>
-      <c r="C642"/>
+      <c r="B642" s="5"/>
+      <c r="C642" s="5"/>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A643"/>
-      <c r="B643"/>
-      <c r="C643"/>
+      <c r="B643" s="5"/>
+      <c r="C643" s="5"/>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A644"/>
-      <c r="B644"/>
-      <c r="C644"/>
+      <c r="B644" s="5"/>
+      <c r="C644" s="5"/>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A645"/>
-      <c r="B645"/>
-      <c r="C645"/>
+      <c r="B645" s="5"/>
+      <c r="C645" s="5"/>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A646"/>
-      <c r="B646"/>
-      <c r="C646"/>
+      <c r="B646" s="5"/>
+      <c r="C646" s="5"/>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A647"/>
-      <c r="B647"/>
-      <c r="C647"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="5"/>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A648"/>
-      <c r="B648"/>
-      <c r="C648"/>
+      <c r="B648" s="5"/>
+      <c r="C648" s="5"/>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A649"/>
-      <c r="B649"/>
-      <c r="C649"/>
+      <c r="B649" s="5"/>
+      <c r="C649" s="5"/>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A650"/>
-      <c r="B650"/>
-      <c r="C650"/>
+      <c r="B650" s="5"/>
+      <c r="C650" s="5"/>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A651"/>
-      <c r="B651"/>
-      <c r="C651"/>
+      <c r="B651" s="5"/>
+      <c r="C651" s="5"/>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A652"/>
-      <c r="B652"/>
-      <c r="C652"/>
+      <c r="B652" s="5"/>
+      <c r="C652" s="5"/>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A653"/>
-      <c r="B653"/>
-      <c r="C653"/>
+      <c r="B653" s="5"/>
+      <c r="C653" s="5"/>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A654"/>
-      <c r="B654"/>
-      <c r="C654"/>
+      <c r="B654" s="5"/>
+      <c r="C654" s="5"/>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A655"/>
-      <c r="B655"/>
-      <c r="C655"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="5"/>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A656"/>
-      <c r="B656"/>
-      <c r="C656"/>
+      <c r="B656" s="5"/>
+      <c r="C656" s="5"/>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A657"/>
-      <c r="B657"/>
-      <c r="C657"/>
+      <c r="B657" s="5"/>
+      <c r="C657" s="5"/>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A658"/>
-      <c r="B658"/>
-      <c r="C658"/>
+      <c r="B658" s="5"/>
+      <c r="C658" s="5"/>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A659"/>
-      <c r="B659"/>
-      <c r="C659"/>
+      <c r="B659" s="5"/>
+      <c r="C659" s="5"/>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A660"/>
-      <c r="B660"/>
-      <c r="C660"/>
+      <c r="B660" s="5"/>
+      <c r="C660" s="5"/>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A661"/>
-      <c r="B661"/>
-      <c r="C661"/>
+      <c r="B661" s="5"/>
+      <c r="C661" s="5"/>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A662"/>
-      <c r="B662"/>
-      <c r="C662"/>
+      <c r="B662" s="5"/>
+      <c r="C662" s="5"/>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A663"/>
-      <c r="B663"/>
-      <c r="C663"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="5"/>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A664"/>
-      <c r="B664"/>
-      <c r="C664"/>
+      <c r="B664" s="5"/>
+      <c r="C664" s="5"/>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A665"/>
-      <c r="B665"/>
-      <c r="C665"/>
+      <c r="B665" s="5"/>
+      <c r="C665" s="5"/>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A666"/>
-      <c r="B666"/>
-      <c r="C666"/>
+      <c r="B666" s="5"/>
+      <c r="C666" s="5"/>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A667"/>
-      <c r="B667"/>
-      <c r="C667"/>
+      <c r="B667" s="5"/>
+      <c r="C667" s="5"/>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A668"/>
-      <c r="B668"/>
-      <c r="C668"/>
+      <c r="B668" s="5"/>
+      <c r="C668" s="5"/>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A669"/>
-      <c r="B669"/>
-      <c r="C669"/>
+      <c r="B669" s="5"/>
+      <c r="C669" s="5"/>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A670"/>
-      <c r="B670"/>
-      <c r="C670"/>
+      <c r="B670" s="5"/>
+      <c r="C670" s="5"/>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A671"/>
-      <c r="B671"/>
-      <c r="C671"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="5"/>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A672"/>
-      <c r="B672"/>
-      <c r="C672"/>
+      <c r="B672" s="5"/>
+      <c r="C672" s="5"/>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A673"/>
-      <c r="B673"/>
-      <c r="C673"/>
+      <c r="B673" s="5"/>
+      <c r="C673" s="5"/>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A674"/>
-      <c r="B674"/>
-      <c r="C674"/>
+      <c r="B674" s="5"/>
+      <c r="C674" s="5"/>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A675"/>
-      <c r="B675"/>
-      <c r="C675"/>
+      <c r="B675" s="5"/>
+      <c r="C675" s="5"/>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A676"/>
-      <c r="B676"/>
-      <c r="C676"/>
+      <c r="B676" s="5"/>
+      <c r="C676" s="5"/>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A677"/>
-      <c r="B677"/>
-      <c r="C677"/>
+      <c r="B677" s="5"/>
+      <c r="C677" s="5"/>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A678"/>
-      <c r="B678"/>
-      <c r="C678"/>
+      <c r="B678" s="5"/>
+      <c r="C678" s="5"/>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A679"/>
-      <c r="B679"/>
-      <c r="C679"/>
+      <c r="B679" s="5"/>
+      <c r="C679" s="5"/>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A680"/>
-      <c r="B680"/>
-      <c r="C680"/>
+      <c r="B680" s="5"/>
+      <c r="C680" s="5"/>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A681"/>
-      <c r="B681"/>
-      <c r="C681"/>
+      <c r="B681" s="5"/>
+      <c r="C681" s="5"/>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A682"/>
-      <c r="B682"/>
-      <c r="C682"/>
+      <c r="B682" s="5"/>
+      <c r="C682" s="5"/>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A683"/>
-      <c r="B683"/>
-      <c r="C683"/>
+      <c r="B683" s="5"/>
+      <c r="C683" s="5"/>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A684"/>
-      <c r="B684"/>
-      <c r="C684"/>
+      <c r="B684" s="5"/>
+      <c r="C684" s="5"/>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A685"/>
-      <c r="B685"/>
-      <c r="C685"/>
+      <c r="B685" s="5"/>
+      <c r="C685" s="5"/>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A686"/>
-      <c r="B686"/>
-      <c r="C686"/>
+      <c r="B686" s="5"/>
+      <c r="C686" s="5"/>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A687"/>
-      <c r="B687"/>
-      <c r="C687"/>
+      <c r="B687" s="5"/>
+      <c r="C687" s="5"/>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A688"/>
-      <c r="B688"/>
-      <c r="C688"/>
+      <c r="B688" s="5"/>
+      <c r="C688" s="5"/>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A689"/>
-      <c r="B689"/>
-      <c r="C689"/>
+      <c r="B689" s="5"/>
+      <c r="C689" s="5"/>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A690"/>
-      <c r="B690"/>
-      <c r="C690"/>
+      <c r="B690" s="5"/>
+      <c r="C690" s="5"/>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A691"/>
-      <c r="B691"/>
-      <c r="C691"/>
+      <c r="B691" s="5"/>
+      <c r="C691" s="5"/>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A692"/>
-      <c r="B692"/>
-      <c r="C692"/>
+      <c r="B692" s="5"/>
+      <c r="C692" s="5"/>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A693"/>
-      <c r="B693"/>
-      <c r="C693"/>
+      <c r="B693" s="5"/>
+      <c r="C693" s="5"/>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A694"/>
-      <c r="B694"/>
-      <c r="C694"/>
+      <c r="B694" s="5"/>
+      <c r="C694" s="5"/>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A695"/>
-      <c r="B695"/>
-      <c r="C695"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="5"/>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A696"/>
-      <c r="B696"/>
-      <c r="C696"/>
+      <c r="B696" s="5"/>
+      <c r="C696" s="5"/>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A697"/>
-      <c r="B697"/>
-      <c r="C697"/>
+      <c r="B697" s="5"/>
+      <c r="C697" s="5"/>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A698"/>
-      <c r="B698"/>
-      <c r="C698"/>
+      <c r="B698" s="5"/>
+      <c r="C698" s="5"/>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A699"/>
-      <c r="B699"/>
-      <c r="C699"/>
+      <c r="B699" s="5"/>
+      <c r="C699" s="5"/>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A700"/>
-      <c r="B700"/>
-      <c r="C700"/>
+      <c r="B700" s="5"/>
+      <c r="C700" s="5"/>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A701"/>
-      <c r="B701"/>
-      <c r="C701"/>
+      <c r="B701" s="5"/>
+      <c r="C701" s="5"/>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A702"/>
-      <c r="B702"/>
-      <c r="C702"/>
+      <c r="B702" s="5"/>
+      <c r="C702" s="5"/>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A703"/>
-      <c r="B703"/>
-      <c r="C703"/>
+      <c r="B703" s="5"/>
+      <c r="C703" s="5"/>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A704"/>
-      <c r="B704"/>
-      <c r="C704"/>
+      <c r="B704" s="5"/>
+      <c r="C704" s="5"/>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A705"/>
-      <c r="B705"/>
-      <c r="C705"/>
+      <c r="B705" s="5"/>
+      <c r="C705" s="5"/>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A706"/>
-      <c r="B706"/>
-      <c r="C706"/>
+      <c r="B706" s="5"/>
+      <c r="C706" s="5"/>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A707"/>
-      <c r="B707"/>
-      <c r="C707"/>
+      <c r="B707" s="5"/>
+      <c r="C707" s="5"/>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A708"/>
-      <c r="B708"/>
-      <c r="C708"/>
+      <c r="B708" s="5"/>
+      <c r="C708" s="5"/>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A709"/>
-      <c r="B709"/>
-      <c r="C709"/>
+      <c r="B709" s="5"/>
+      <c r="C709" s="5"/>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A710"/>
-      <c r="B710"/>
-      <c r="C710"/>
+      <c r="B710" s="5"/>
+      <c r="C710" s="5"/>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A711"/>
-      <c r="B711"/>
-      <c r="C711"/>
+      <c r="B711" s="5"/>
+      <c r="C711" s="5"/>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A712"/>
-      <c r="B712"/>
-      <c r="C712"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="5"/>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A713"/>
-      <c r="B713"/>
-      <c r="C713"/>
+      <c r="B713" s="5"/>
+      <c r="C713" s="5"/>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A714"/>
-      <c r="B714"/>
-      <c r="C714"/>
+      <c r="B714" s="5"/>
+      <c r="C714" s="5"/>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A715"/>
-      <c r="B715"/>
-      <c r="C715"/>
+      <c r="B715" s="5"/>
+      <c r="C715" s="5"/>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A716"/>
-      <c r="B716"/>
-      <c r="C716"/>
+      <c r="B716" s="5"/>
+      <c r="C716" s="5"/>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A717"/>
-      <c r="B717"/>
-      <c r="C717"/>
+      <c r="B717" s="5"/>
+      <c r="C717" s="5"/>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A718"/>
-      <c r="B718"/>
-      <c r="C718"/>
+      <c r="B718" s="5"/>
+      <c r="C718" s="5"/>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A719"/>
-      <c r="B719"/>
-      <c r="C719"/>
+      <c r="B719" s="5"/>
+      <c r="C719" s="5"/>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A720"/>
-      <c r="B720"/>
-      <c r="C720"/>
+      <c r="B720" s="5"/>
+      <c r="C720" s="5"/>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A721"/>
-      <c r="B721"/>
-      <c r="C721"/>
+      <c r="B721" s="5"/>
+      <c r="C721" s="5"/>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A722"/>
-      <c r="B722"/>
-      <c r="C722"/>
+      <c r="B722" s="5"/>
+      <c r="C722" s="5"/>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A723"/>
-      <c r="B723"/>
-      <c r="C723"/>
+      <c r="B723" s="5"/>
+      <c r="C723" s="5"/>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A724"/>
-      <c r="B724"/>
-      <c r="C724"/>
+      <c r="B724" s="5"/>
+      <c r="C724" s="5"/>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A725"/>
-      <c r="B725"/>
-      <c r="C725"/>
+      <c r="B725" s="5"/>
+      <c r="C725" s="5"/>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A726"/>
-      <c r="B726"/>
-      <c r="C726"/>
+      <c r="B726" s="5"/>
+      <c r="C726" s="5"/>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A727"/>
-      <c r="B727"/>
-      <c r="C727"/>
+      <c r="B727" s="5"/>
+      <c r="C727" s="5"/>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A728"/>
-      <c r="B728"/>
-      <c r="C728"/>
+      <c r="B728" s="5"/>
+      <c r="C728" s="5"/>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A729"/>
-      <c r="B729"/>
-      <c r="C729"/>
+      <c r="B729" s="5"/>
+      <c r="C729" s="5"/>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A730"/>
-      <c r="B730"/>
-      <c r="C730"/>
+      <c r="B730" s="5"/>
+      <c r="C730" s="5"/>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A731"/>
-      <c r="B731"/>
-      <c r="C731"/>
+      <c r="B731" s="5"/>
+      <c r="C731" s="5"/>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A732"/>
-      <c r="B732"/>
-      <c r="C732"/>
+      <c r="B732" s="5"/>
+      <c r="C732" s="5"/>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A733"/>
-      <c r="B733"/>
-      <c r="C733"/>
+      <c r="B733" s="5"/>
+      <c r="C733" s="5"/>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A734"/>
-      <c r="B734"/>
-      <c r="C734"/>
+      <c r="B734" s="5"/>
+      <c r="C734" s="5"/>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A735"/>
-      <c r="B735"/>
-      <c r="C735"/>
+      <c r="B735" s="5"/>
+      <c r="C735" s="5"/>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A736"/>
-      <c r="B736"/>
-      <c r="C736"/>
+      <c r="B736" s="5"/>
+      <c r="C736" s="5"/>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A737"/>
-      <c r="B737"/>
-      <c r="C737"/>
+      <c r="B737" s="5"/>
+      <c r="C737" s="5"/>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A738"/>
-      <c r="B738"/>
-      <c r="C738"/>
+      <c r="B738" s="5"/>
+      <c r="C738" s="5"/>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A739"/>
-      <c r="B739"/>
-      <c r="C739"/>
+      <c r="B739" s="5"/>
+      <c r="C739" s="5"/>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A740"/>
-      <c r="B740"/>
-      <c r="C740"/>
+      <c r="B740" s="5"/>
+      <c r="C740" s="5"/>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A741"/>
-      <c r="B741"/>
-      <c r="C741"/>
+      <c r="B741" s="5"/>
+      <c r="C741" s="5"/>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A742"/>
-      <c r="B742"/>
-      <c r="C742"/>
+      <c r="B742" s="5"/>
+      <c r="C742" s="5"/>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A743"/>
-      <c r="B743"/>
-      <c r="C743"/>
+      <c r="B743" s="5"/>
+      <c r="C743" s="5"/>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A744"/>
-      <c r="B744"/>
-      <c r="C744"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="5"/>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A745"/>
-      <c r="B745"/>
-      <c r="C745"/>
+      <c r="B745" s="5"/>
+      <c r="C745" s="5"/>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A746"/>
-      <c r="B746"/>
-      <c r="C746"/>
+      <c r="B746" s="5"/>
+      <c r="C746" s="5"/>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A747"/>
-      <c r="B747"/>
-      <c r="C747"/>
+      <c r="B747" s="5"/>
+      <c r="C747" s="5"/>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A748"/>
-      <c r="B748"/>
-      <c r="C748"/>
+      <c r="B748" s="5"/>
+      <c r="C748" s="5"/>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A749"/>
-      <c r="B749"/>
-      <c r="C749"/>
+      <c r="B749" s="5"/>
+      <c r="C749" s="5"/>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A750"/>
-      <c r="B750"/>
-      <c r="C750"/>
+      <c r="B750" s="5"/>
+      <c r="C750" s="5"/>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A751"/>
-      <c r="B751"/>
-      <c r="C751"/>
+      <c r="B751" s="5"/>
+      <c r="C751" s="5"/>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A752"/>
-      <c r="B752"/>
-      <c r="C752"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="5"/>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A753"/>
-      <c r="B753"/>
-      <c r="C753"/>
+      <c r="B753" s="5"/>
+      <c r="C753" s="5"/>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A754"/>
-      <c r="B754"/>
-      <c r="C754"/>
+      <c r="B754" s="5"/>
+      <c r="C754" s="5"/>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A755"/>
-      <c r="B755"/>
-      <c r="C755"/>
+      <c r="B755" s="5"/>
+      <c r="C755" s="5"/>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A756"/>
-      <c r="B756"/>
-      <c r="C756"/>
+      <c r="B756" s="5"/>
+      <c r="C756" s="5"/>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A757"/>
-      <c r="B757"/>
-      <c r="C757"/>
+      <c r="B757" s="5"/>
+      <c r="C757" s="5"/>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A758"/>
-      <c r="B758"/>
-      <c r="C758"/>
+      <c r="B758" s="5"/>
+      <c r="C758" s="5"/>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A759"/>
-      <c r="B759"/>
-      <c r="C759"/>
+      <c r="B759" s="5"/>
+      <c r="C759" s="5"/>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A760"/>
-      <c r="B760"/>
-      <c r="C760"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="5"/>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A761"/>
-      <c r="B761"/>
-      <c r="C761"/>
+      <c r="B761" s="5"/>
+      <c r="C761" s="5"/>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A762"/>
-      <c r="B762"/>
-      <c r="C762"/>
+      <c r="B762" s="5"/>
+      <c r="C762" s="5"/>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A763"/>
-      <c r="B763"/>
-      <c r="C763"/>
+      <c r="B763" s="5"/>
+      <c r="C763" s="5"/>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A764"/>
-      <c r="B764"/>
-      <c r="C764"/>
+      <c r="B764" s="5"/>
+      <c r="C764" s="5"/>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A765"/>
-      <c r="B765"/>
-      <c r="C765"/>
+      <c r="B765" s="5"/>
+      <c r="C765" s="5"/>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A766"/>
-      <c r="B766"/>
-      <c r="C766"/>
+      <c r="B766" s="5"/>
+      <c r="C766" s="5"/>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A767"/>
-      <c r="B767"/>
-      <c r="C767"/>
+      <c r="B767" s="5"/>
+      <c r="C767" s="5"/>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A768"/>
-      <c r="B768"/>
-      <c r="C768"/>
+      <c r="B768" s="5"/>
+      <c r="C768" s="5"/>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A769"/>
-      <c r="B769"/>
-      <c r="C769"/>
+      <c r="B769" s="5"/>
+      <c r="C769" s="5"/>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A770"/>
-      <c r="B770"/>
-      <c r="C770"/>
+      <c r="B770" s="5"/>
+      <c r="C770" s="5"/>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A771"/>
-      <c r="B771"/>
-      <c r="C771"/>
+      <c r="B771" s="5"/>
+      <c r="C771" s="5"/>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A772"/>
-      <c r="B772"/>
-      <c r="C772"/>
+      <c r="B772" s="5"/>
+      <c r="C772" s="5"/>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A773"/>
-      <c r="B773"/>
-      <c r="C773"/>
+      <c r="B773" s="5"/>
+      <c r="C773" s="5"/>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A774"/>
-      <c r="B774"/>
-      <c r="C774"/>
+      <c r="B774" s="5"/>
+      <c r="C774" s="5"/>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A775"/>
-      <c r="B775"/>
-      <c r="C775"/>
+      <c r="B775" s="5"/>
+      <c r="C775" s="5"/>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A776"/>
-      <c r="B776"/>
-      <c r="C776"/>
+      <c r="B776" s="5"/>
+      <c r="C776" s="5"/>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A777"/>
-      <c r="B777"/>
-      <c r="C777"/>
+      <c r="B777" s="5"/>
+      <c r="C777" s="5"/>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A778"/>
-      <c r="B778"/>
-      <c r="C778"/>
+      <c r="B778" s="5"/>
+      <c r="C778" s="5"/>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A779"/>
-      <c r="B779"/>
-      <c r="C779"/>
+      <c r="B779" s="5"/>
+      <c r="C779" s="5"/>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A780"/>
-      <c r="B780"/>
-      <c r="C780"/>
+      <c r="B780" s="5"/>
+      <c r="C780" s="5"/>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A781"/>
-      <c r="B781"/>
-      <c r="C781"/>
+      <c r="B781" s="5"/>
+      <c r="C781" s="5"/>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A782"/>
-      <c r="B782"/>
-      <c r="C782"/>
+      <c r="B782" s="5"/>
+      <c r="C782" s="5"/>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A783"/>
-      <c r="B783"/>
-      <c r="C783"/>
+      <c r="B783" s="5"/>
+      <c r="C783" s="5"/>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A784"/>
-      <c r="B784"/>
-      <c r="C784"/>
+      <c r="B784" s="5"/>
+      <c r="C784" s="5"/>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A785"/>
-      <c r="B785"/>
-      <c r="C785"/>
+      <c r="B785" s="5"/>
+      <c r="C785" s="5"/>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A786"/>
-      <c r="B786"/>
-      <c r="C786"/>
+      <c r="B786" s="5"/>
+      <c r="C786" s="5"/>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A787"/>
-      <c r="B787"/>
-      <c r="C787"/>
+      <c r="B787" s="5"/>
+      <c r="C787" s="5"/>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A788"/>
-      <c r="B788"/>
-      <c r="C788"/>
+      <c r="B788" s="5"/>
+      <c r="C788" s="5"/>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A789"/>
-      <c r="B789"/>
-      <c r="C789"/>
+      <c r="B789" s="5"/>
+      <c r="C789" s="5"/>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A790"/>
-      <c r="B790"/>
-      <c r="C790"/>
+      <c r="B790" s="5"/>
+      <c r="C790" s="5"/>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A791"/>
-      <c r="B791"/>
-      <c r="C791"/>
+      <c r="B791" s="5"/>
+      <c r="C791" s="5"/>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A792"/>
-      <c r="B792"/>
-      <c r="C792"/>
+      <c r="B792" s="5"/>
+      <c r="C792" s="5"/>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A793"/>
-      <c r="B793"/>
-      <c r="C793"/>
+      <c r="B793" s="5"/>
+      <c r="C793" s="5"/>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A794"/>
-      <c r="B794"/>
-      <c r="C794"/>
+      <c r="B794" s="5"/>
+      <c r="C794" s="5"/>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A795"/>
-      <c r="B795"/>
-      <c r="C795"/>
+      <c r="B795" s="5"/>
+      <c r="C795" s="5"/>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A796"/>
-      <c r="B796"/>
-      <c r="C796"/>
+      <c r="B796" s="5"/>
+      <c r="C796" s="5"/>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A797"/>
-      <c r="B797"/>
-      <c r="C797"/>
+      <c r="B797" s="5"/>
+      <c r="C797" s="5"/>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A798"/>
-      <c r="B798"/>
-      <c r="C798"/>
+      <c r="B798" s="5"/>
+      <c r="C798" s="5"/>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A799"/>
-      <c r="B799"/>
-      <c r="C799"/>
+      <c r="B799" s="5"/>
+      <c r="C799" s="5"/>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A800"/>
-      <c r="B800"/>
-      <c r="C800"/>
+      <c r="B800" s="5"/>
+      <c r="C800" s="5"/>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A801"/>
-      <c r="B801"/>
-      <c r="C801"/>
+      <c r="B801" s="5"/>
+      <c r="C801" s="5"/>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A802"/>
-      <c r="B802"/>
-      <c r="C802"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="5"/>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A803"/>
-      <c r="B803"/>
-      <c r="C803"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="5"/>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A804"/>
-      <c r="B804"/>
-      <c r="C804"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="5"/>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A805"/>
-      <c r="B805"/>
-      <c r="C805"/>
+      <c r="B805" s="5"/>
+      <c r="C805" s="5"/>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A806"/>
-      <c r="B806"/>
-      <c r="C806"/>
+      <c r="B806" s="5"/>
+      <c r="C806" s="5"/>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A807"/>
-      <c r="B807"/>
-      <c r="C807"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="5"/>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A808"/>
-      <c r="B808"/>
-      <c r="C808"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="5"/>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A809"/>
-      <c r="B809"/>
-      <c r="C809"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="5"/>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A810"/>
-      <c r="B810"/>
-      <c r="C810"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="5"/>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A811"/>
-      <c r="B811"/>
-      <c r="C811"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="5"/>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A812"/>
-      <c r="B812"/>
-      <c r="C812"/>
+      <c r="B812" s="5"/>
+      <c r="C812" s="5"/>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A813"/>
-      <c r="B813"/>
-      <c r="C813"/>
+      <c r="B813" s="5"/>
+      <c r="C813" s="5"/>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A814"/>
-      <c r="B814"/>
-      <c r="C814"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="5"/>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A815"/>
-      <c r="B815"/>
-      <c r="C815"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="5"/>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A816"/>
-      <c r="B816"/>
-      <c r="C816"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="5"/>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A817"/>
-      <c r="B817"/>
-      <c r="C817"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="5"/>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A818"/>
-      <c r="B818"/>
-      <c r="C818"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="5"/>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A819"/>
-      <c r="B819"/>
-      <c r="C819"/>
+      <c r="B819" s="5"/>
+      <c r="C819" s="5"/>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A820"/>
-      <c r="B820"/>
-      <c r="C820"/>
+      <c r="B820" s="5"/>
+      <c r="C820" s="5"/>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A821"/>
-      <c r="B821"/>
-      <c r="C821"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="5"/>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A822"/>
-      <c r="B822"/>
-      <c r="C822"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="5"/>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A823"/>
-      <c r="B823"/>
-      <c r="C823"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="5"/>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A824"/>
-      <c r="B824"/>
-      <c r="C824"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="5"/>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A825"/>
-      <c r="B825"/>
-      <c r="C825"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="5"/>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A826"/>
-      <c r="B826"/>
-      <c r="C826"/>
+      <c r="B826" s="5"/>
+      <c r="C826" s="5"/>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A827"/>
-      <c r="B827"/>
-      <c r="C827"/>
+      <c r="B827" s="5"/>
+      <c r="C827" s="5"/>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A828"/>
-      <c r="B828"/>
-      <c r="C828"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="5"/>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A829"/>
-      <c r="B829"/>
-      <c r="C829"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="5"/>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A830"/>
-      <c r="B830"/>
-      <c r="C830"/>
+      <c r="B830" s="5"/>
+      <c r="C830" s="5"/>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A831"/>
-      <c r="B831"/>
-      <c r="C831"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="5"/>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A832"/>
-      <c r="B832"/>
-      <c r="C832"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="5"/>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A833"/>
-      <c r="B833"/>
-      <c r="C833"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="5"/>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A834"/>
-      <c r="B834"/>
-      <c r="C834"/>
+      <c r="B834" s="5"/>
+      <c r="C834" s="5"/>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A835"/>
-      <c r="B835"/>
-      <c r="C835"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="5"/>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A836"/>
-      <c r="B836"/>
-      <c r="C836"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="5"/>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A837"/>
-      <c r="B837"/>
-      <c r="C837"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="5"/>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A838"/>
-      <c r="B838"/>
-      <c r="C838"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="5"/>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A839"/>
-      <c r="B839"/>
-      <c r="C839"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="5"/>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A840"/>
-      <c r="B840"/>
-      <c r="C840"/>
+      <c r="B840" s="5"/>
+      <c r="C840" s="5"/>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A841"/>
-      <c r="B841"/>
-      <c r="C841"/>
+      <c r="B841" s="5"/>
+      <c r="C841" s="5"/>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A842"/>
-      <c r="B842"/>
-      <c r="C842"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="5"/>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A843"/>
-      <c r="B843"/>
-      <c r="C843"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="5"/>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A844"/>
-      <c r="B844"/>
-      <c r="C844"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="5"/>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A845"/>
-      <c r="B845"/>
-      <c r="C845"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="5"/>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A846"/>
-      <c r="B846"/>
-      <c r="C846"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="5"/>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A847"/>
-      <c r="B847"/>
-      <c r="C847"/>
+      <c r="B847" s="5"/>
+      <c r="C847" s="5"/>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A848"/>
-      <c r="B848"/>
-      <c r="C848"/>
+      <c r="B848" s="5"/>
+      <c r="C848" s="5"/>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A849"/>
-      <c r="B849"/>
-      <c r="C849"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="5"/>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A850"/>
-      <c r="B850"/>
-      <c r="C850"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="5"/>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A851"/>
-      <c r="B851"/>
-      <c r="C851"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="5"/>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A852"/>
-      <c r="B852"/>
-      <c r="C852"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="5"/>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A853"/>
-      <c r="B853"/>
-      <c r="C853"/>
+      <c r="B853" s="5"/>
+      <c r="C853" s="5"/>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A854"/>
-      <c r="B854"/>
-      <c r="C854"/>
+      <c r="B854" s="5"/>
+      <c r="C854" s="5"/>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A855"/>
-      <c r="B855"/>
-      <c r="C855"/>
+      <c r="B855" s="5"/>
+      <c r="C855" s="5"/>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A856"/>
-      <c r="B856"/>
-      <c r="C856"/>
+      <c r="B856" s="5"/>
+      <c r="C856" s="5"/>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A857"/>
-      <c r="B857"/>
-      <c r="C857"/>
+      <c r="B857" s="5"/>
+      <c r="C857" s="5"/>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A858"/>
-      <c r="B858"/>
-      <c r="C858"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="5"/>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A859"/>
-      <c r="B859"/>
-      <c r="C859"/>
+      <c r="B859" s="5"/>
+      <c r="C859" s="5"/>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A860"/>
-      <c r="B860"/>
-      <c r="C860"/>
+      <c r="B860" s="5"/>
+      <c r="C860" s="5"/>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A861"/>
-      <c r="B861"/>
-      <c r="C861"/>
+      <c r="B861" s="5"/>
+      <c r="C861" s="5"/>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A862"/>
-      <c r="B862"/>
-      <c r="C862"/>
+      <c r="B862" s="5"/>
+      <c r="C862" s="5"/>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A863"/>
-      <c r="B863"/>
-      <c r="C863"/>
+      <c r="B863" s="5"/>
+      <c r="C863" s="5"/>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A864"/>
-      <c r="B864"/>
-      <c r="C864"/>
+      <c r="B864" s="5"/>
+      <c r="C864" s="5"/>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A865"/>
-      <c r="B865"/>
-      <c r="C865"/>
+      <c r="B865" s="5"/>
+      <c r="C865" s="5"/>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A866"/>
-      <c r="B866"/>
-      <c r="C866"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="5"/>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A867"/>
-      <c r="B867"/>
-      <c r="C867"/>
+      <c r="B867" s="5"/>
+      <c r="C867" s="5"/>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A868"/>
-      <c r="B868"/>
-      <c r="C868"/>
+      <c r="B868" s="5"/>
+      <c r="C868" s="5"/>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A869"/>
-      <c r="B869"/>
-      <c r="C869"/>
+      <c r="B869" s="5"/>
+      <c r="C869" s="5"/>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A870"/>
-      <c r="B870"/>
-      <c r="C870"/>
+      <c r="B870" s="5"/>
+      <c r="C870" s="5"/>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A871"/>
-      <c r="B871"/>
-      <c r="C871"/>
+      <c r="B871" s="5"/>
+      <c r="C871" s="5"/>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A872"/>
-      <c r="B872"/>
-      <c r="C872"/>
+      <c r="B872" s="5"/>
+      <c r="C872" s="5"/>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A873"/>
-      <c r="B873"/>
-      <c r="C873"/>
+      <c r="B873" s="5"/>
+      <c r="C873" s="5"/>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A874"/>
-      <c r="B874"/>
-      <c r="C874"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="5"/>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A875"/>
-      <c r="B875"/>
-      <c r="C875"/>
+      <c r="B875" s="5"/>
+      <c r="C875" s="5"/>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A876"/>
-      <c r="B876"/>
-      <c r="C876"/>
+      <c r="B876" s="5"/>
+      <c r="C876" s="5"/>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A877"/>
-      <c r="B877"/>
-      <c r="C877"/>
+      <c r="B877" s="5"/>
+      <c r="C877" s="5"/>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A878"/>
-      <c r="B878"/>
-      <c r="C878"/>
+      <c r="B878" s="5"/>
+      <c r="C878" s="5"/>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A879"/>
-      <c r="B879"/>
-      <c r="C879"/>
+      <c r="B879" s="5"/>
+      <c r="C879" s="5"/>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A880"/>
-      <c r="B880"/>
-      <c r="C880"/>
+      <c r="B880" s="5"/>
+      <c r="C880" s="5"/>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A881"/>
-      <c r="B881"/>
-      <c r="C881"/>
+      <c r="B881" s="5"/>
+      <c r="C881" s="5"/>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A882"/>
-      <c r="B882"/>
-      <c r="C882"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="5"/>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A883"/>
-      <c r="B883"/>
-      <c r="C883"/>
+      <c r="B883" s="5"/>
+      <c r="C883" s="5"/>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A884"/>
-      <c r="B884"/>
-      <c r="C884"/>
+      <c r="B884" s="5"/>
+      <c r="C884" s="5"/>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A885"/>
-      <c r="B885"/>
-      <c r="C885"/>
+      <c r="B885" s="5"/>
+      <c r="C885" s="5"/>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A886"/>
-      <c r="B886"/>
-      <c r="C886"/>
+      <c r="B886" s="5"/>
+      <c r="C886" s="5"/>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A887"/>
-      <c r="B887"/>
-      <c r="C887"/>
+      <c r="B887" s="5"/>
+      <c r="C887" s="5"/>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A888"/>
-      <c r="B888"/>
-      <c r="C888"/>
+      <c r="B888" s="5"/>
+      <c r="C888" s="5"/>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A889"/>
-      <c r="B889"/>
-      <c r="C889"/>
+      <c r="B889" s="5"/>
+      <c r="C889" s="5"/>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A890"/>
-      <c r="B890"/>
-      <c r="C890"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="5"/>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A891"/>
-      <c r="B891"/>
-      <c r="C891"/>
+      <c r="B891" s="5"/>
+      <c r="C891" s="5"/>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A892"/>
-      <c r="B892"/>
-      <c r="C892"/>
+      <c r="B892" s="5"/>
+      <c r="C892" s="5"/>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A893"/>
-      <c r="B893"/>
-      <c r="C893"/>
+      <c r="B893" s="5"/>
+      <c r="C893" s="5"/>
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A894"/>
-      <c r="B894"/>
-      <c r="C894"/>
+      <c r="B894" s="5"/>
+      <c r="C894" s="5"/>
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A895"/>
-      <c r="B895"/>
-      <c r="C895"/>
+      <c r="B895" s="5"/>
+      <c r="C895" s="5"/>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A896"/>
-      <c r="B896"/>
-      <c r="C896"/>
+      <c r="B896" s="5"/>
+      <c r="C896" s="5"/>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A897"/>
-      <c r="B897"/>
-      <c r="C897"/>
+      <c r="B897" s="5"/>
+      <c r="C897" s="5"/>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A898"/>
-      <c r="B898"/>
-      <c r="C898"/>
+      <c r="B898" s="5"/>
+      <c r="C898" s="5"/>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A899"/>
-      <c r="B899"/>
-      <c r="C899"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="5"/>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A900"/>
-      <c r="B900"/>
-      <c r="C900"/>
+      <c r="B900" s="5"/>
+      <c r="C900" s="5"/>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A901"/>
-      <c r="B901"/>
-      <c r="C901"/>
+      <c r="B901" s="5"/>
+      <c r="C901" s="5"/>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A902"/>
-      <c r="B902"/>
-      <c r="C902"/>
+      <c r="B902" s="5"/>
+      <c r="C902" s="5"/>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A903"/>
-      <c r="B903"/>
-      <c r="C903"/>
+      <c r="B903" s="5"/>
+      <c r="C903" s="5"/>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A904"/>
-      <c r="B904"/>
-      <c r="C904"/>
+      <c r="B904" s="5"/>
+      <c r="C904" s="5"/>
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A905"/>
-      <c r="B905"/>
-      <c r="C905"/>
+      <c r="B905" s="5"/>
+      <c r="C905" s="5"/>
     </row>
     <row r="906" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A906"/>
-      <c r="B906"/>
-      <c r="C906"/>
+      <c r="B906" s="5"/>
+      <c r="C906" s="5"/>
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A907"/>
-      <c r="B907"/>
-      <c r="C907"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="5"/>
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A908"/>
-      <c r="B908"/>
-      <c r="C908"/>
+      <c r="B908" s="5"/>
+      <c r="C908" s="5"/>
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A909"/>
-      <c r="B909"/>
-      <c r="C909"/>
+      <c r="B909" s="5"/>
+      <c r="C909" s="5"/>
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A910"/>
-      <c r="B910"/>
-      <c r="C910"/>
+      <c r="B910" s="5"/>
+      <c r="C910" s="5"/>
     </row>
     <row r="911" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A911"/>
-      <c r="B911"/>
-      <c r="C911"/>
+      <c r="B911" s="5"/>
+      <c r="C911" s="5"/>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A912"/>
-      <c r="B912"/>
-      <c r="C912"/>
+      <c r="B912" s="5"/>
+      <c r="C912" s="5"/>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A913"/>
-      <c r="B913"/>
-      <c r="C913"/>
+      <c r="B913" s="5"/>
+      <c r="C913" s="5"/>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A914"/>
-      <c r="B914"/>
-      <c r="C914"/>
+      <c r="B914" s="5"/>
+      <c r="C914" s="5"/>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A915"/>
-      <c r="B915"/>
-      <c r="C915"/>
+      <c r="B915" s="5"/>
+      <c r="C915" s="5"/>
     </row>
     <row r="916" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A916"/>
-      <c r="B916"/>
-      <c r="C916"/>
+      <c r="B916" s="5"/>
+      <c r="C916" s="5"/>
     </row>
     <row r="917" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A917"/>
-      <c r="B917"/>
-      <c r="C917"/>
+      <c r="B917" s="5"/>
+      <c r="C917" s="5"/>
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A918"/>
-      <c r="B918"/>
-      <c r="C918"/>
+      <c r="B918" s="5"/>
+      <c r="C918" s="5"/>
     </row>
     <row r="919" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A919"/>
-      <c r="B919"/>
-      <c r="C919"/>
+      <c r="B919" s="5"/>
+      <c r="C919" s="5"/>
     </row>
     <row r="920" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A920"/>
-      <c r="B920"/>
-      <c r="C920"/>
+      <c r="B920" s="5"/>
+      <c r="C920" s="5"/>
     </row>
     <row r="921" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A921"/>
-      <c r="B921"/>
-      <c r="C921"/>
+      <c r="B921" s="5"/>
+      <c r="C921" s="5"/>
     </row>
     <row r="922" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A922"/>
-      <c r="B922"/>
-      <c r="C922"/>
+      <c r="B922" s="5"/>
+      <c r="C922" s="5"/>
     </row>
     <row r="923" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A923"/>
-      <c r="B923"/>
-      <c r="C923"/>
+      <c r="B923" s="5"/>
+      <c r="C923" s="5"/>
     </row>
     <row r="924" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A924"/>
-      <c r="B924"/>
-      <c r="C924"/>
+      <c r="B924" s="5"/>
+      <c r="C924" s="5"/>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A925"/>
-      <c r="B925"/>
-      <c r="C925"/>
+      <c r="B925" s="5"/>
+      <c r="C925" s="5"/>
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A926"/>
-      <c r="B926"/>
-      <c r="C926"/>
+      <c r="B926" s="5"/>
+      <c r="C926" s="5"/>
     </row>
     <row r="927" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A927"/>
-      <c r="B927"/>
-      <c r="C927"/>
+      <c r="B927" s="5"/>
+      <c r="C927" s="5"/>
     </row>
     <row r="928" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A928"/>
-      <c r="B928"/>
-      <c r="C928"/>
+      <c r="B928" s="5"/>
+      <c r="C928" s="5"/>
     </row>
     <row r="929" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A929"/>
-      <c r="B929"/>
-      <c r="C929"/>
+      <c r="B929" s="5"/>
+      <c r="C929" s="5"/>
     </row>
     <row r="930" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A930"/>
-      <c r="B930"/>
-      <c r="C930"/>
+      <c r="B930" s="5"/>
+      <c r="C930" s="5"/>
     </row>
     <row r="931" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A931"/>
-      <c r="B931"/>
-      <c r="C931"/>
+      <c r="B931" s="5"/>
+      <c r="C931" s="5"/>
     </row>
     <row r="932" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A932"/>
-      <c r="B932"/>
-      <c r="C932"/>
+      <c r="B932" s="5"/>
+      <c r="C932" s="5"/>
     </row>
     <row r="933" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A933"/>
-      <c r="B933"/>
-      <c r="C933"/>
+      <c r="B933" s="5"/>
+      <c r="C933" s="5"/>
     </row>
     <row r="934" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A934"/>
-      <c r="B934"/>
-      <c r="C934"/>
+      <c r="B934" s="5"/>
+      <c r="C934" s="5"/>
     </row>
     <row r="935" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A935"/>
-      <c r="B935"/>
-      <c r="C935"/>
+      <c r="B935" s="5"/>
+      <c r="C935" s="5"/>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A936"/>
-      <c r="B936"/>
-      <c r="C936"/>
+      <c r="B936" s="5"/>
+      <c r="C936" s="5"/>
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A937"/>
-      <c r="B937"/>
-      <c r="C937"/>
+      <c r="B937" s="5"/>
+      <c r="C937" s="5"/>
     </row>
     <row r="938" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A938"/>
-      <c r="B938"/>
-      <c r="C938"/>
+      <c r="B938" s="5"/>
+      <c r="C938" s="5"/>
     </row>
     <row r="939" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A939"/>
-      <c r="B939"/>
-      <c r="C939"/>
+      <c r="B939" s="5"/>
+      <c r="C939" s="5"/>
     </row>
     <row r="940" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A940"/>
-      <c r="B940"/>
-      <c r="C940"/>
+      <c r="B940" s="5"/>
+      <c r="C940" s="5"/>
     </row>
     <row r="941" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A941"/>
-      <c r="B941"/>
-      <c r="C941"/>
+      <c r="B941" s="5"/>
+      <c r="C941" s="5"/>
     </row>
     <row r="942" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A942"/>
-      <c r="B942"/>
-      <c r="C942"/>
+      <c r="B942" s="5"/>
+      <c r="C942" s="5"/>
     </row>
     <row r="943" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A943"/>
-      <c r="B943"/>
-      <c r="C943"/>
+      <c r="B943" s="5"/>
+      <c r="C943" s="5"/>
     </row>
     <row r="944" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A944"/>
-      <c r="B944"/>
-      <c r="C944"/>
+      <c r="B944" s="5"/>
+      <c r="C944" s="5"/>
     </row>
     <row r="945" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A945"/>
-      <c r="B945"/>
-      <c r="C945"/>
+      <c r="B945" s="5"/>
+      <c r="C945" s="5"/>
     </row>
     <row r="946" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A946"/>
-      <c r="B946"/>
-      <c r="C946"/>
+      <c r="B946" s="5"/>
+      <c r="C946" s="5"/>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A947"/>
-      <c r="B947"/>
-      <c r="C947"/>
+      <c r="B947" s="5"/>
+      <c r="C947" s="5"/>
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A948"/>
-      <c r="B948"/>
-      <c r="C948"/>
+      <c r="B948" s="5"/>
+      <c r="C948" s="5"/>
     </row>
     <row r="949" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A949"/>
-      <c r="B949"/>
-      <c r="C949"/>
+      <c r="B949" s="5"/>
+      <c r="C949" s="5"/>
     </row>
     <row r="950" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A950"/>
-      <c r="B950"/>
-      <c r="C950"/>
+      <c r="B950" s="5"/>
+      <c r="C950" s="5"/>
     </row>
     <row r="951" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A951"/>
-      <c r="B951"/>
-      <c r="C951"/>
+      <c r="B951" s="5"/>
+      <c r="C951" s="5"/>
     </row>
     <row r="952" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A952"/>
-      <c r="B952"/>
-      <c r="C952"/>
+      <c r="B952" s="5"/>
+      <c r="C952" s="5"/>
     </row>
     <row r="953" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A953"/>
-      <c r="B953"/>
-      <c r="C953"/>
+      <c r="B953" s="5"/>
+      <c r="C953" s="5"/>
     </row>
     <row r="954" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A954"/>
-      <c r="B954"/>
-      <c r="C954"/>
+      <c r="B954" s="5"/>
+      <c r="C954" s="5"/>
     </row>
     <row r="955" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A955"/>
-      <c r="B955"/>
-      <c r="C955"/>
+      <c r="B955" s="5"/>
+      <c r="C955" s="5"/>
     </row>
     <row r="956" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A956"/>
-      <c r="B956"/>
-      <c r="C956"/>
+      <c r="B956" s="5"/>
+      <c r="C956" s="5"/>
     </row>
     <row r="957" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A957"/>
-      <c r="B957"/>
-      <c r="C957"/>
+      <c r="B957" s="5"/>
+      <c r="C957" s="5"/>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A958"/>
-      <c r="B958"/>
-      <c r="C958"/>
+      <c r="B958" s="5"/>
+      <c r="C958" s="5"/>
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A959"/>
-      <c r="B959"/>
-      <c r="C959"/>
+      <c r="B959" s="5"/>
+      <c r="C959" s="5"/>
     </row>
     <row r="960" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A960"/>
-      <c r="B960"/>
-      <c r="C960"/>
+      <c r="B960" s="5"/>
+      <c r="C960" s="5"/>
     </row>
     <row r="961" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A961"/>
-      <c r="B961"/>
-      <c r="C961"/>
+      <c r="B961" s="5"/>
+      <c r="C961" s="5"/>
     </row>
     <row r="962" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A962"/>
-      <c r="B962"/>
-      <c r="C962"/>
+      <c r="B962" s="5"/>
+      <c r="C962" s="5"/>
     </row>
     <row r="963" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A963"/>
-      <c r="B963"/>
-      <c r="C963"/>
+      <c r="B963" s="5"/>
+      <c r="C963" s="5"/>
     </row>
     <row r="964" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A964"/>
-      <c r="B964"/>
-      <c r="C964"/>
+      <c r="B964" s="5"/>
+      <c r="C964" s="5"/>
     </row>
     <row r="965" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A965"/>
-      <c r="B965"/>
-      <c r="C965"/>
+      <c r="B965" s="5"/>
+      <c r="C965" s="5"/>
     </row>
     <row r="966" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A966"/>
-      <c r="B966"/>
-      <c r="C966"/>
+      <c r="B966" s="5"/>
+      <c r="C966" s="5"/>
     </row>
     <row r="967" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A967"/>
-      <c r="B967"/>
-      <c r="C967"/>
+      <c r="B967" s="5"/>
+      <c r="C967" s="5"/>
     </row>
     <row r="968" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A968"/>
-      <c r="B968"/>
-      <c r="C968"/>
+      <c r="B968" s="5"/>
+      <c r="C968" s="5"/>
     </row>
     <row r="969" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A969"/>
-      <c r="B969"/>
-      <c r="C969"/>
+      <c r="B969" s="5"/>
+      <c r="C969" s="5"/>
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A970"/>
-      <c r="B970"/>
-      <c r="C970"/>
+      <c r="B970" s="5"/>
+      <c r="C970" s="5"/>
     </row>
     <row r="971" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A971"/>
-      <c r="B971"/>
-      <c r="C971"/>
+      <c r="B971" s="5"/>
+      <c r="C971" s="5"/>
     </row>
     <row r="972" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A972"/>
-      <c r="B972"/>
-      <c r="C972"/>
+      <c r="B972" s="5"/>
+      <c r="C972" s="5"/>
     </row>
     <row r="973" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A973"/>
-      <c r="B973"/>
-      <c r="C973"/>
+      <c r="B973" s="5"/>
+      <c r="C973" s="5"/>
     </row>
     <row r="974" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A974"/>
-      <c r="B974"/>
-      <c r="C974"/>
+      <c r="B974" s="5"/>
+      <c r="C974" s="5"/>
     </row>
     <row r="975" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A975"/>
-      <c r="B975"/>
-      <c r="C975"/>
+      <c r="B975" s="5"/>
+      <c r="C975" s="5"/>
     </row>
     <row r="976" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A976"/>
-      <c r="B976"/>
-      <c r="C976"/>
+      <c r="B976" s="5"/>
+      <c r="C976" s="5"/>
     </row>
     <row r="977" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A977"/>
-      <c r="B977"/>
-      <c r="C977"/>
+      <c r="B977" s="5"/>
+      <c r="C977" s="5"/>
     </row>
     <row r="978" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A978"/>
-      <c r="B978"/>
-      <c r="C978"/>
+      <c r="B978" s="5"/>
+      <c r="C978" s="5"/>
     </row>
     <row r="979" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A979"/>
-      <c r="B979"/>
-      <c r="C979"/>
+      <c r="B979" s="5"/>
+      <c r="C979" s="5"/>
     </row>
     <row r="980" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A980"/>
-      <c r="B980"/>
-      <c r="C980"/>
+      <c r="B980" s="5"/>
+      <c r="C980" s="5"/>
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A981"/>
-      <c r="B981"/>
-      <c r="C981"/>
+      <c r="B981" s="5"/>
+      <c r="C981" s="5"/>
     </row>
     <row r="982" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A982"/>
-      <c r="B982"/>
-      <c r="C982"/>
+      <c r="B982" s="5"/>
+      <c r="C982" s="5"/>
     </row>
     <row r="983" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A983"/>
-      <c r="B983"/>
-      <c r="C983"/>
+      <c r="B983" s="5"/>
+      <c r="C983" s="5"/>
     </row>
     <row r="984" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A984"/>
-      <c r="B984"/>
-      <c r="C984"/>
+      <c r="B984" s="5"/>
+      <c r="C984" s="5"/>
     </row>
     <row r="985" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A985"/>
-      <c r="B985"/>
-      <c r="C985"/>
+      <c r="B985" s="5"/>
+      <c r="C985" s="5"/>
     </row>
     <row r="986" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A986"/>
-      <c r="B986"/>
-      <c r="C986"/>
+      <c r="B986" s="5"/>
+      <c r="C986" s="5"/>
     </row>
     <row r="987" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A987"/>
-      <c r="B987"/>
-      <c r="C987"/>
+      <c r="B987" s="5"/>
+      <c r="C987" s="5"/>
     </row>
     <row r="988" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A988"/>
-      <c r="B988"/>
-      <c r="C988"/>
+      <c r="B988" s="5"/>
+      <c r="C988" s="5"/>
     </row>
     <row r="989" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A989"/>
-      <c r="B989"/>
-      <c r="C989"/>
+      <c r="B989" s="5"/>
+      <c r="C989" s="5"/>
     </row>
     <row r="990" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A990"/>
-      <c r="B990"/>
-      <c r="C990"/>
+      <c r="B990" s="5"/>
+      <c r="C990" s="5"/>
     </row>
     <row r="991" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A991"/>
-      <c r="B991"/>
-      <c r="C991"/>
+      <c r="B991" s="5"/>
+      <c r="C991" s="5"/>
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A992"/>
-      <c r="B992"/>
-      <c r="C992"/>
+      <c r="B992" s="5"/>
+      <c r="C992" s="5"/>
     </row>
     <row r="993" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A993"/>
-      <c r="B993"/>
-      <c r="C993"/>
+      <c r="B993" s="5"/>
+      <c r="C993" s="5"/>
     </row>
     <row r="994" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A994"/>
-      <c r="B994"/>
-      <c r="C994"/>
+      <c r="B994" s="5"/>
+      <c r="C994" s="5"/>
     </row>
     <row r="995" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A995"/>
-      <c r="B995"/>
-      <c r="C995"/>
+      <c r="B995" s="5"/>
+      <c r="C995" s="5"/>
     </row>
     <row r="996" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A996"/>
-      <c r="B996"/>
-      <c r="C996"/>
+      <c r="B996" s="5"/>
+      <c r="C996" s="5"/>
     </row>
     <row r="997" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A997"/>
-      <c r="B997"/>
-      <c r="C997"/>
+      <c r="B997" s="5"/>
+      <c r="C997" s="5"/>
     </row>
     <row r="998" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A998"/>
-      <c r="B998"/>
-      <c r="C998"/>
+      <c r="B998" s="5"/>
+      <c r="C998" s="5"/>
     </row>
     <row r="999" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A999"/>
-      <c r="B999"/>
-      <c r="C999"/>
+      <c r="B999" s="5"/>
+      <c r="C999" s="5"/>
     </row>
     <row r="1000" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1000"/>
-      <c r="B1000"/>
-      <c r="C1000"/>
+      <c r="B1000" s="5"/>
+      <c r="C1000" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>